--- a/ssp_modeling/tableau/data/WaterScenarios.xlsx
+++ b/ssp_modeling/tableau/data/WaterScenarios.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_libya/ssp_modeling/tableau/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817669E4-6AC3-AD42-88D6-549626915CFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F8A124-F17D-B943-BE78-389778374660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-51200" yWindow="600" windowWidth="25600" windowHeight="28200" xr2:uid="{023BFEE8-2E9B-BC48-8927-6C5415905B12}"/>
   </bookViews>
@@ -18,6 +18,7 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -169,11 +170,1100 @@
           <cell r="C122">
             <v>6039.6921628399505</v>
           </cell>
+        </row>
+        <row r="202">
+          <cell r="C202">
+            <v>784.22197749500003</v>
+          </cell>
+          <cell r="D202">
+            <v>389.62701858989999</v>
+          </cell>
+          <cell r="E202">
+            <v>5865.68538653</v>
+          </cell>
+          <cell r="F202">
+            <v>0</v>
+          </cell>
+          <cell r="G202">
+            <v>7039.5343826149001</v>
+          </cell>
+        </row>
+        <row r="203">
+          <cell r="C203">
+            <v>794.86617439858742</v>
+          </cell>
+          <cell r="D203">
+            <v>403.93296803511453</v>
+          </cell>
+          <cell r="E203">
+            <v>5927.3744477185592</v>
+          </cell>
+          <cell r="F203">
+            <v>0</v>
+          </cell>
+          <cell r="G203">
+            <v>7126.1735901522607</v>
+          </cell>
+        </row>
+        <row r="204">
+          <cell r="C204">
+            <v>805.38432378370169</v>
+          </cell>
+          <cell r="D204">
+            <v>418.62357806823337</v>
+          </cell>
+          <cell r="E204">
+            <v>5987.7010800633643</v>
+          </cell>
+          <cell r="F204">
+            <v>0</v>
+          </cell>
+          <cell r="G204">
+            <v>7211.7089819152989</v>
+          </cell>
+        </row>
+        <row r="205">
+          <cell r="C205">
+            <v>815.77742002060484</v>
+          </cell>
+          <cell r="D205">
+            <v>433.70798901525569</v>
+          </cell>
+          <cell r="E205">
+            <v>6046.6831343259983</v>
+          </cell>
+          <cell r="F205">
+            <v>0</v>
+          </cell>
+          <cell r="G205">
+            <v>7296.1685433618586</v>
+          </cell>
+        </row>
+        <row r="206">
+          <cell r="C206">
+            <v>826.0464506870444</v>
+          </cell>
+          <cell r="D206">
+            <v>449.19554435252496</v>
+          </cell>
+          <cell r="E206">
+            <v>6104.3382628513064</v>
+          </cell>
+          <cell r="F206">
+            <v>0</v>
+          </cell>
+          <cell r="G206">
+            <v>7379.5802578908751</v>
+          </cell>
+        </row>
+        <row r="207">
+          <cell r="C207">
+            <v>836.19239661131905</v>
+          </cell>
+          <cell r="D207">
+            <v>465.09579503632892</v>
+          </cell>
+          <cell r="E207">
+            <v>6160.6839215996133</v>
+          </cell>
+          <cell r="F207">
+            <v>0</v>
+          </cell>
+          <cell r="G207">
+            <v>7461.9721132472614</v>
+          </cell>
+        </row>
+        <row r="208">
+          <cell r="C208">
+            <v>846.21623191508377</v>
+          </cell>
+          <cell r="D208">
+            <v>481.41850392215304</v>
+          </cell>
+          <cell r="E208">
+            <v>6215.737372159123</v>
+          </cell>
+          <cell r="F208">
+            <v>0</v>
+          </cell>
+          <cell r="G208">
+            <v>7543.3721079963598</v>
+          </cell>
+        </row>
+        <row r="209">
+          <cell r="C209">
+            <v>856.11892405589538</v>
+          </cell>
+          <cell r="D209">
+            <v>498.17365027540257</v>
+          </cell>
+          <cell r="E209">
+            <v>6269.5156837386994</v>
+          </cell>
+          <cell r="F209">
+            <v>54.75</v>
+          </cell>
+          <cell r="G209">
+            <v>7678.5582580699975</v>
+          </cell>
+        </row>
+        <row r="210">
+          <cell r="C210">
+            <v>865.90143386950137</v>
+          </cell>
+          <cell r="D210">
+            <v>515.37143437544944</v>
+          </cell>
+          <cell r="E210">
+            <v>6322.035735141184</v>
+          </cell>
+          <cell r="F210">
+            <v>109.5</v>
+          </cell>
+          <cell r="G210">
+            <v>7812.8086033861346</v>
+          </cell>
+        </row>
+        <row r="211">
+          <cell r="C211">
+            <v>875.56471561186947</v>
+          </cell>
+          <cell r="D211">
+            <v>533.02228221489327</v>
+          </cell>
+          <cell r="E211">
+            <v>6373.3142167174701</v>
+          </cell>
+          <cell r="F211">
+            <v>164.25</v>
+          </cell>
+          <cell r="G211">
+            <v>7946.151214544233</v>
+          </cell>
+        </row>
+        <row r="212">
+          <cell r="C212">
+            <v>885.10971700096752</v>
+          </cell>
+          <cell r="D212">
+            <v>551.13685029596729</v>
+          </cell>
+          <cell r="E212">
+            <v>6423.3676323014861</v>
+          </cell>
+          <cell r="F212">
+            <v>219</v>
+          </cell>
+          <cell r="G212">
+            <v>8078.6141995984208</v>
+          </cell>
+        </row>
+        <row r="213">
+          <cell r="C213">
+            <v>894.53737925828398</v>
+          </cell>
+          <cell r="D213">
+            <v>569.72603052605507</v>
+          </cell>
+          <cell r="E213">
+            <v>6472.2123011262884</v>
+          </cell>
+          <cell r="F213">
+            <v>273.75</v>
+          </cell>
+          <cell r="G213">
+            <v>8210.2257109106285</v>
+          </cell>
+        </row>
+        <row r="214">
+          <cell r="C214">
+            <v>903.84863715010238</v>
+          </cell>
+          <cell r="D214">
+            <v>588.80095521432304</v>
+          </cell>
+          <cell r="E214">
+            <v>6519.8643597214268</v>
+          </cell>
+          <cell r="F214">
+            <v>328.5</v>
+          </cell>
+          <cell r="G214">
+            <v>8341.013952085852</v>
+          </cell>
+        </row>
+        <row r="215">
+          <cell r="C215">
+            <v>913.04441902852136</v>
+          </cell>
+          <cell r="D215">
+            <v>608.3730021715196</v>
+          </cell>
+          <cell r="E215">
+            <v>6566.3397637917687</v>
+          </cell>
+          <cell r="F215">
+            <v>383.25</v>
+          </cell>
+          <cell r="G215">
+            <v>8471.0071849918095</v>
+          </cell>
+        </row>
+        <row r="216">
+          <cell r="C216">
+            <v>922.12564687222732</v>
+          </cell>
+          <cell r="D216">
+            <v>628.45379991502341</v>
+          </cell>
+          <cell r="E216">
+            <v>6611.654290077965</v>
+          </cell>
+          <cell r="F216">
+            <v>438</v>
+          </cell>
+          <cell r="G216">
+            <v>8600.2337368652152</v>
+          </cell>
+        </row>
+        <row r="217">
+          <cell r="C217">
+            <v>931.09323632702035</v>
+          </cell>
+          <cell r="D217">
+            <v>649.05523298127218</v>
+          </cell>
+          <cell r="E217">
+            <v>6655.8235381986988</v>
+          </cell>
+          <cell r="F217">
+            <v>492.75</v>
+          </cell>
+          <cell r="G217">
+            <v>8728.7220075069908</v>
+          </cell>
+        </row>
+        <row r="218">
+          <cell r="C218">
+            <v>939.9480967460936</v>
+          </cell>
+          <cell r="D218">
+            <v>670.18944734774129</v>
+          </cell>
+          <cell r="E218">
+            <v>6698.8629324749354</v>
+          </cell>
+          <cell r="F218">
+            <v>547.5</v>
+          </cell>
+          <cell r="G218">
+            <v>8856.50047656877</v>
+          </cell>
+        </row>
+        <row r="219">
+          <cell r="C219">
+            <v>948.69113123006798</v>
+          </cell>
+          <cell r="D219">
+            <v>691.86885596669049</v>
+          </cell>
+          <cell r="E219">
+            <v>6740.7877237363109</v>
+          </cell>
+          <cell r="F219">
+            <v>547.5</v>
+          </cell>
+          <cell r="G219">
+            <v>8928.8477109330688</v>
+          </cell>
+        </row>
+        <row r="220">
+          <cell r="C220">
+            <v>957.32323666678394</v>
+          </cell>
+          <cell r="D220">
+            <v>714.10614441293103</v>
+          </cell>
+          <cell r="E220">
+            <v>6781.6129911098215</v>
+          </cell>
+          <cell r="F220">
+            <v>547.5</v>
+          </cell>
+          <cell r="G220">
+            <v>9000.5423721895368</v>
+          </cell>
+        </row>
+        <row r="221">
+          <cell r="C221">
+            <v>965.84530377085218</v>
+          </cell>
+          <cell r="D221">
+            <v>736.91427664792297</v>
+          </cell>
+          <cell r="E221">
+            <v>6821.353643791037</v>
+          </cell>
+          <cell r="F221">
+            <v>547.5</v>
+          </cell>
+          <cell r="G221">
+            <v>9071.613224209812</v>
+          </cell>
+        </row>
+        <row r="222">
+          <cell r="C222">
+            <v>974.25821712296306</v>
+          </cell>
+          <cell r="D222">
+            <v>760.30650090254744</v>
+          </cell>
+          <cell r="E222">
+            <v>6860.0244227979247</v>
+          </cell>
+          <cell r="F222">
+            <v>547.5</v>
+          </cell>
+          <cell r="G222">
+            <v>9142.0891408234347</v>
+          </cell>
+        </row>
+        <row r="223">
+          <cell r="C223">
+            <v>982.56285520895824</v>
+          </cell>
+          <cell r="D223">
+            <v>784.29635568095091</v>
+          </cell>
+          <cell r="E223">
+            <v>6897.6399027074976</v>
+          </cell>
+          <cell r="F223">
+            <v>547.5</v>
+          </cell>
+          <cell r="G223">
+            <v>9211.9991135974069</v>
+          </cell>
+        </row>
+        <row r="224">
+          <cell r="C224">
+            <v>990.76009045866579</v>
+          </cell>
+          <cell r="D224">
+            <v>808.89767588790824</v>
+          </cell>
+          <cell r="E224">
+            <v>6934.2144933754589</v>
+          </cell>
+          <cell r="F224">
+            <v>547.5</v>
+          </cell>
+          <cell r="G224">
+            <v>9281.372259722033</v>
+          </cell>
+        </row>
+        <row r="225">
+          <cell r="C225">
+            <v>998.8507892844957</v>
+          </cell>
+          <cell r="D225">
+            <v>834.12459908219046</v>
+          </cell>
+          <cell r="E225">
+            <v>6969.7624416389599</v>
+          </cell>
+          <cell r="F225">
+            <v>547.5</v>
+          </cell>
+          <cell r="G225">
+            <v>9350.2378300056462</v>
+          </cell>
+        </row>
+        <row r="226">
+          <cell r="C226">
+            <v>1006.8358121198061</v>
+          </cell>
+          <cell r="D226">
+            <v>859.99157185848537</v>
+          </cell>
+          <cell r="E226">
+            <v>7004.2978330026699</v>
+          </cell>
+          <cell r="F226">
+            <v>547.5</v>
+          </cell>
+          <cell r="G226">
+            <v>9418.6252169809613</v>
+          </cell>
+        </row>
+        <row r="227">
+          <cell r="C227">
+            <v>1014.7160134570314</v>
+          </cell>
+          <cell r="D227">
+            <v>886.51335636045974</v>
+          </cell>
+          <cell r="E227">
+            <v>7037.8345933082928</v>
+          </cell>
+          <cell r="F227">
+            <v>547.5</v>
+          </cell>
+          <cell r="G227">
+            <v>9486.5639631257836</v>
+          </cell>
+        </row>
+        <row r="228">
+          <cell r="C228">
+            <v>1022.4922418855811</v>
+          </cell>
+          <cell r="D228">
+            <v>913.7050369276069</v>
+          </cell>
+          <cell r="E228">
+            <v>7070.3864903877156</v>
+          </cell>
+          <cell r="F228">
+            <v>547.5</v>
+          </cell>
+          <cell r="G228">
+            <v>9554.0837692009045</v>
+          </cell>
+        </row>
+        <row r="229">
+          <cell r="C229">
+            <v>1030.1653401295089</v>
+          </cell>
+          <cell r="D229">
+            <v>941.58202687857829</v>
+          </cell>
+          <cell r="E229">
+            <v>7101.9671356998942</v>
+          </cell>
+          <cell r="F229">
+            <v>547.5</v>
+          </cell>
+          <cell r="G229">
+            <v>9621.2145027079823</v>
+          </cell>
+        </row>
+        <row r="230">
+          <cell r="C230">
+            <v>1037.7361450849505</v>
+          </cell>
+          <cell r="D230">
+            <v>970.16007543374485</v>
+          </cell>
+          <cell r="E230">
+            <v>7132.5899859516949</v>
+          </cell>
+          <cell r="F230">
+            <v>547.5</v>
+          </cell>
+          <cell r="G230">
+            <v>9687.9862064703902</v>
+          </cell>
+        </row>
+        <row r="231">
+          <cell r="C231">
+            <v>1045.2054878573344</v>
+          </cell>
+          <cell r="D231">
+            <v>999.45527477979738</v>
+          </cell>
+          <cell r="E231">
+            <v>7162.268344702783</v>
+          </cell>
+          <cell r="F231">
+            <v>547.5</v>
+          </cell>
+          <cell r="G231">
+            <v>9754.4291073399145</v>
+          </cell>
+        </row>
+        <row r="232">
+          <cell r="C232">
+            <v>1052.5741937983671</v>
+          </cell>
+          <cell r="D232">
+            <v>1029.4840672792445</v>
+          </cell>
+          <cell r="E232">
+            <v>7191.0153639547507</v>
+          </cell>
+          <cell r="F232">
+            <v>547.5</v>
+          </cell>
+          <cell r="G232">
+            <v>9820.5736250323625</v>
+          </cell>
+        </row>
+        <row r="233">
+          <cell r="C233">
+            <v>784.22197749500003</v>
+          </cell>
+          <cell r="D233">
+            <v>389.62701858989999</v>
+          </cell>
+          <cell r="E233">
+            <v>5865.68538653</v>
+          </cell>
+          <cell r="F233">
+            <v>0</v>
+          </cell>
+          <cell r="G233">
+            <v>7039.5343826149001</v>
+          </cell>
+        </row>
+        <row r="234">
+          <cell r="C234">
+            <v>794.86617439858742</v>
+          </cell>
+          <cell r="D234">
+            <v>403.93296803511453</v>
+          </cell>
+          <cell r="E234">
+            <v>5927.3744477185592</v>
+          </cell>
+          <cell r="F234">
+            <v>0</v>
+          </cell>
+          <cell r="G234">
+            <v>7126.1735901522607</v>
+          </cell>
+        </row>
+        <row r="235">
+          <cell r="C235">
+            <v>805.38432378370169</v>
+          </cell>
+          <cell r="D235">
+            <v>418.62357806823337</v>
+          </cell>
+          <cell r="E235">
+            <v>5987.7010800633643</v>
+          </cell>
+          <cell r="F235">
+            <v>0</v>
+          </cell>
+          <cell r="G235">
+            <v>7211.7089819152989</v>
+          </cell>
+        </row>
+        <row r="236">
+          <cell r="C236">
+            <v>815.77742002060484</v>
+          </cell>
+          <cell r="D236">
+            <v>433.70798901525569</v>
+          </cell>
+          <cell r="E236">
+            <v>6046.6831343259983</v>
+          </cell>
+          <cell r="F236">
+            <v>0</v>
+          </cell>
+          <cell r="G236">
+            <v>7296.1685433618586</v>
+          </cell>
+        </row>
+        <row r="237">
+          <cell r="C237">
+            <v>826.0464506870444</v>
+          </cell>
+          <cell r="D237">
+            <v>449.19554435252496</v>
+          </cell>
+          <cell r="E237">
+            <v>6104.3382628513064</v>
+          </cell>
+          <cell r="F237">
+            <v>0</v>
+          </cell>
+          <cell r="G237">
+            <v>7379.5802578908751</v>
+          </cell>
+        </row>
+        <row r="238">
+          <cell r="C238">
+            <v>836.19239661131905</v>
+          </cell>
+          <cell r="D238">
+            <v>465.09579503632892</v>
+          </cell>
+          <cell r="E238">
+            <v>6160.6839215996133</v>
+          </cell>
+          <cell r="F238">
+            <v>0</v>
+          </cell>
+          <cell r="G238">
+            <v>7461.9721132472614</v>
+          </cell>
+        </row>
+        <row r="239">
+          <cell r="C239">
+            <v>846.21623191508377</v>
+          </cell>
+          <cell r="D239">
+            <v>481.41850392215304</v>
+          </cell>
+          <cell r="E239">
+            <v>6215.737372159123</v>
+          </cell>
+          <cell r="F239">
+            <v>0</v>
+          </cell>
+          <cell r="G239">
+            <v>7543.3721079963598</v>
+          </cell>
+        </row>
+        <row r="240">
+          <cell r="C240">
+            <v>856.11892405589538</v>
+          </cell>
+          <cell r="D240">
+            <v>498.17365027540257</v>
+          </cell>
+          <cell r="E240">
+            <v>6269.5156837386994</v>
+          </cell>
+          <cell r="F240">
+            <v>0</v>
+          </cell>
+          <cell r="G240">
+            <v>7623.8082580699975</v>
+          </cell>
+        </row>
+        <row r="241">
+          <cell r="C241">
+            <v>865.90143386950137</v>
+          </cell>
+          <cell r="D241">
+            <v>515.37143437544944</v>
+          </cell>
+          <cell r="E241">
+            <v>6322.035735141184</v>
+          </cell>
+          <cell r="F241">
+            <v>0</v>
+          </cell>
+          <cell r="G241">
+            <v>7703.3086033861346</v>
+          </cell>
+        </row>
+        <row r="242">
+          <cell r="C242">
+            <v>875.56471561186947</v>
+          </cell>
+          <cell r="D242">
+            <v>533.02228221489327</v>
+          </cell>
+          <cell r="E242">
+            <v>6373.3142167174701</v>
+          </cell>
+          <cell r="F242">
+            <v>0</v>
+          </cell>
+          <cell r="G242">
+            <v>7781.901214544233</v>
+          </cell>
+        </row>
+        <row r="243">
+          <cell r="C243">
+            <v>885.10971700096752</v>
+          </cell>
+          <cell r="D243">
+            <v>551.13685029596729</v>
+          </cell>
+          <cell r="E243">
+            <v>6423.3676323014861</v>
+          </cell>
+          <cell r="F243">
+            <v>0</v>
+          </cell>
+          <cell r="G243">
+            <v>7859.6141995984208</v>
+          </cell>
+        </row>
+        <row r="244">
+          <cell r="C244">
+            <v>894.53737925828398</v>
+          </cell>
+          <cell r="D244">
+            <v>569.72603052605507</v>
+          </cell>
+          <cell r="E244">
+            <v>6472.2123011262884</v>
+          </cell>
+          <cell r="F244">
+            <v>0</v>
+          </cell>
+          <cell r="G244">
+            <v>7936.4757109106276</v>
+          </cell>
+        </row>
+        <row r="245">
+          <cell r="C245">
+            <v>903.84863715010238</v>
+          </cell>
+          <cell r="D245">
+            <v>588.80095521432304</v>
+          </cell>
+          <cell r="E245">
+            <v>6519.8643597214268</v>
+          </cell>
+          <cell r="F245">
+            <v>0</v>
+          </cell>
+          <cell r="G245">
+            <v>8012.513952085852</v>
+          </cell>
+        </row>
+        <row r="246">
+          <cell r="C246">
+            <v>913.04441902852136</v>
+          </cell>
+          <cell r="D246">
+            <v>608.3730021715196</v>
+          </cell>
+          <cell r="E246">
+            <v>6566.3397637917687</v>
+          </cell>
+          <cell r="F246">
+            <v>0</v>
+          </cell>
+          <cell r="G246">
+            <v>8087.7571849918095</v>
+          </cell>
+        </row>
+        <row r="247">
+          <cell r="C247">
+            <v>922.12564687222732</v>
+          </cell>
+          <cell r="D247">
+            <v>628.45379991502341</v>
+          </cell>
+          <cell r="E247">
+            <v>6611.654290077965</v>
+          </cell>
+          <cell r="F247">
+            <v>0</v>
+          </cell>
+          <cell r="G247">
+            <v>8162.2337368652152</v>
+          </cell>
+        </row>
+        <row r="248">
+          <cell r="C248">
+            <v>931.09323632702035</v>
+          </cell>
+          <cell r="D248">
+            <v>649.05523298127218</v>
+          </cell>
+          <cell r="E248">
+            <v>6655.8235381986988</v>
+          </cell>
+          <cell r="F248">
+            <v>0</v>
+          </cell>
+          <cell r="G248">
+            <v>8235.9720075069908</v>
+          </cell>
+        </row>
+        <row r="249">
+          <cell r="C249">
+            <v>939.9480967460936</v>
+          </cell>
+          <cell r="D249">
+            <v>670.18944734774129</v>
+          </cell>
+          <cell r="E249">
+            <v>6698.8629324749354</v>
+          </cell>
+          <cell r="F249">
+            <v>0</v>
+          </cell>
+          <cell r="G249">
+            <v>8309.00047656877</v>
+          </cell>
+        </row>
+        <row r="250">
+          <cell r="C250">
+            <v>948.69113123006798</v>
+          </cell>
+          <cell r="D250">
+            <v>691.86885596669049</v>
+          </cell>
+          <cell r="E250">
+            <v>6740.7877237363109</v>
+          </cell>
+          <cell r="F250">
+            <v>0</v>
+          </cell>
+          <cell r="G250">
+            <v>8381.3477109330688</v>
+          </cell>
+        </row>
+        <row r="251">
+          <cell r="C251">
+            <v>957.32323666678394</v>
+          </cell>
+          <cell r="D251">
+            <v>714.10614441293103</v>
+          </cell>
+          <cell r="E251">
+            <v>6781.6129911098215</v>
+          </cell>
+          <cell r="F251">
+            <v>0</v>
+          </cell>
+          <cell r="G251">
+            <v>8453.0423721895368</v>
+          </cell>
+        </row>
+        <row r="252">
+          <cell r="C252">
+            <v>965.84530377085218</v>
+          </cell>
+          <cell r="D252">
+            <v>736.91427664792297</v>
+          </cell>
+          <cell r="E252">
+            <v>6821.353643791037</v>
+          </cell>
+          <cell r="F252">
+            <v>0</v>
+          </cell>
+          <cell r="G252">
+            <v>8524.113224209812</v>
+          </cell>
+        </row>
+        <row r="253">
+          <cell r="C253">
+            <v>974.25821712296306</v>
+          </cell>
+          <cell r="D253">
+            <v>760.30650090254744</v>
+          </cell>
+          <cell r="E253">
+            <v>6860.0244227979247</v>
+          </cell>
+          <cell r="F253">
+            <v>0</v>
+          </cell>
+          <cell r="G253">
+            <v>8594.5891408234347</v>
+          </cell>
+        </row>
+        <row r="254">
+          <cell r="C254">
+            <v>982.56285520895824</v>
+          </cell>
+          <cell r="D254">
+            <v>784.29635568095091</v>
+          </cell>
+          <cell r="E254">
+            <v>6897.6399027074976</v>
+          </cell>
+          <cell r="F254">
+            <v>0</v>
+          </cell>
+          <cell r="G254">
+            <v>8664.4991135974069</v>
+          </cell>
+        </row>
+        <row r="255">
+          <cell r="C255">
+            <v>990.76009045866579</v>
+          </cell>
+          <cell r="D255">
+            <v>808.89767588790824</v>
+          </cell>
+          <cell r="E255">
+            <v>6934.2144933754589</v>
+          </cell>
+          <cell r="F255">
+            <v>0</v>
+          </cell>
+          <cell r="G255">
+            <v>8733.872259722033</v>
+          </cell>
+        </row>
+        <row r="256">
+          <cell r="C256">
+            <v>998.8507892844957</v>
+          </cell>
+          <cell r="D256">
+            <v>834.12459908219046</v>
+          </cell>
+          <cell r="E256">
+            <v>6969.7624416389599</v>
+          </cell>
+          <cell r="F256">
+            <v>0</v>
+          </cell>
+          <cell r="G256">
+            <v>8802.7378300056462</v>
+          </cell>
+        </row>
+        <row r="257">
+          <cell r="C257">
+            <v>1006.8358121198061</v>
+          </cell>
+          <cell r="D257">
+            <v>859.99157185848537</v>
+          </cell>
+          <cell r="E257">
+            <v>7004.2978330026699</v>
+          </cell>
+          <cell r="F257">
+            <v>0</v>
+          </cell>
+          <cell r="G257">
+            <v>8871.1252169809613</v>
+          </cell>
+        </row>
+        <row r="258">
+          <cell r="C258">
+            <v>1014.7160134570314</v>
+          </cell>
+          <cell r="D258">
+            <v>886.51335636045974</v>
+          </cell>
+          <cell r="E258">
+            <v>7037.8345933082928</v>
+          </cell>
+          <cell r="F258">
+            <v>0</v>
+          </cell>
+          <cell r="G258">
+            <v>8939.0639631257836</v>
+          </cell>
+        </row>
+        <row r="259">
+          <cell r="C259">
+            <v>1022.4922418855811</v>
+          </cell>
+          <cell r="D259">
+            <v>913.7050369276069</v>
+          </cell>
+          <cell r="E259">
+            <v>7070.3864903877156</v>
+          </cell>
+          <cell r="F259">
+            <v>0</v>
+          </cell>
+          <cell r="G259">
+            <v>9006.5837692009045</v>
+          </cell>
+        </row>
+        <row r="260">
+          <cell r="C260">
+            <v>1030.1653401295089</v>
+          </cell>
+          <cell r="D260">
+            <v>941.58202687857829</v>
+          </cell>
+          <cell r="E260">
+            <v>7101.9671356998942</v>
+          </cell>
+          <cell r="F260">
+            <v>0</v>
+          </cell>
+          <cell r="G260">
+            <v>9073.7145027079823</v>
+          </cell>
+        </row>
+        <row r="261">
+          <cell r="C261">
+            <v>1037.7361450849505</v>
+          </cell>
+          <cell r="D261">
+            <v>970.16007543374485</v>
+          </cell>
+          <cell r="E261">
+            <v>7132.5899859516949</v>
+          </cell>
+          <cell r="F261">
+            <v>0</v>
+          </cell>
+          <cell r="G261">
+            <v>9140.4862064703902</v>
+          </cell>
+        </row>
+        <row r="262">
+          <cell r="C262">
+            <v>1045.2054878573344</v>
+          </cell>
+          <cell r="D262">
+            <v>999.45527477979738</v>
+          </cell>
+          <cell r="E262">
+            <v>7162.268344702783</v>
+          </cell>
+          <cell r="F262">
+            <v>0</v>
+          </cell>
+          <cell r="G262">
+            <v>9206.9291073399145</v>
+          </cell>
+        </row>
+        <row r="263">
+          <cell r="C263">
+            <v>1052.5741937983671</v>
+          </cell>
+          <cell r="D263">
+            <v>1029.4840672792445</v>
+          </cell>
+          <cell r="E263">
+            <v>7191.0153639547507</v>
+          </cell>
+          <cell r="F263">
+            <v>0</v>
+          </cell>
+          <cell r="G263">
+            <v>9273.0736250323625</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="README"/>
+      <sheetName val="Inputs"/>
+      <sheetName val="Demand"/>
+      <sheetName val="Supply"/>
+      <sheetName val="Energy"/>
+      <sheetName val="Investment"/>
+      <sheetName val="Summary"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6">
+        <row r="122">
+          <cell r="C122">
+            <v>6059.6921628399505</v>
+          </cell>
           <cell r="D122">
             <v>912</v>
           </cell>
           <cell r="E122">
-            <v>20</v>
+            <v>0</v>
           </cell>
           <cell r="F122">
             <v>7.8422197749500002</v>
@@ -184,13 +1274,13 @@
         </row>
         <row r="123">
           <cell r="C123">
-            <v>6111.7231117650917</v>
+            <v>6156.0564450984248</v>
           </cell>
           <cell r="D123">
             <v>893.76</v>
           </cell>
           <cell r="E123">
-            <v>44.333333333333329</v>
+            <v>0</v>
           </cell>
           <cell r="F123">
             <v>16.95714505383653</v>
@@ -201,13 +1291,13 @@
         </row>
         <row r="124">
           <cell r="C124">
-            <v>6182.0422940050321</v>
+            <v>6250.7089606716991</v>
           </cell>
           <cell r="D124">
             <v>875.88479999999993</v>
           </cell>
           <cell r="E124">
-            <v>68.666666666666657</v>
+            <v>0</v>
           </cell>
           <cell r="F124">
             <v>26.30922124360092</v>
@@ -218,13 +1308,13 @@
         </row>
         <row r="125">
           <cell r="C125">
-            <v>6250.689292880953</v>
+            <v>6343.689292880953</v>
           </cell>
           <cell r="D125">
             <v>858.36710399999993</v>
           </cell>
           <cell r="E125">
-            <v>93</v>
+            <v>0</v>
           </cell>
           <cell r="F125">
             <v>35.894206480906618</v>
@@ -235,13 +1325,13 @@
         </row>
         <row r="126">
           <cell r="C126">
-            <v>6317.7034984328593</v>
+            <v>6435.0368317661923</v>
           </cell>
           <cell r="D126">
             <v>841.1997619199999</v>
           </cell>
           <cell r="E126">
-            <v>117.33333333333333</v>
+            <v>0</v>
           </cell>
           <cell r="F126">
             <v>45.707903604683125</v>
@@ -252,13 +1342,13 @@
         </row>
         <row r="127">
           <cell r="C127">
-            <v>6383.1241171309066</v>
+            <v>6524.7907837975736</v>
           </cell>
           <cell r="D127">
             <v>824.37576668159988</v>
           </cell>
           <cell r="E127">
-            <v>141.66666666666669</v>
+            <v>0</v>
           </cell>
           <cell r="F127">
             <v>55.746159774087921</v>
@@ -269,13 +1359,13 @@
         </row>
         <row r="128">
           <cell r="C128">
-            <v>6446.9901815949561</v>
+            <v>6612.9901815949561</v>
           </cell>
           <cell r="D128">
             <v>807.88825134796787</v>
           </cell>
           <cell r="E128">
-            <v>166</v>
+            <v>0</v>
           </cell>
           <cell r="F128">
             <v>66.004866089376534</v>
@@ -286,13 +1376,13 @@
         </row>
         <row r="129">
           <cell r="C129">
-            <v>6564.090560325576</v>
+            <v>6739.6984046017715</v>
           </cell>
           <cell r="D129">
             <v>791.73048632100847</v>
           </cell>
           <cell r="E129">
-            <v>190.33333333333334</v>
+            <v>14.725489057137942</v>
           </cell>
           <cell r="F129">
             <v>76.479957215659979</v>
@@ -303,13 +1393,13 @@
         </row>
         <row r="130">
           <cell r="C130">
-            <v>6679.7139674496757</v>
+            <v>6830.7888039146947</v>
           </cell>
           <cell r="D130">
             <v>775.89587659458823</v>
           </cell>
           <cell r="E130">
-            <v>214.66666666666666</v>
+            <v>63.591830201647646</v>
           </cell>
           <cell r="F130">
             <v>87.1674110095298</v>
@@ -320,13 +1410,13 @@
         </row>
         <row r="131">
           <cell r="C131">
-            <v>6793.8989724839885</v>
+            <v>6920.6224940027096</v>
           </cell>
           <cell r="D131">
             <v>760.3779590626965</v>
           </cell>
           <cell r="E131">
-            <v>239</v>
+            <v>112.27647848127944</v>
           </cell>
           <cell r="F131">
             <v>98.063248148529368</v>
@@ -337,13 +1427,13 @@
         </row>
         <row r="132">
           <cell r="C132">
-            <v>6906.684010119664</v>
+            <v>7009.2378937268386</v>
           </cell>
           <cell r="D132">
             <v>745.17039988144245</v>
           </cell>
           <cell r="E132">
-            <v>263.33333333333337</v>
+            <v>160.77944972615859</v>
           </cell>
           <cell r="F132">
             <v>109.16353176345264</v>
@@ -354,13 +1444,13 @@
         </row>
         <row r="133">
           <cell r="C133">
-            <v>7018.1073900311767</v>
+            <v>7096.6732670272604</v>
           </cell>
           <cell r="D133">
             <v>730.2669918838136</v>
           </cell>
           <cell r="E133">
-            <v>287.66666666666669</v>
+            <v>209.10078967058243</v>
           </cell>
           <cell r="F133">
             <v>120.4643670734489</v>
@@ -371,13 +1461,13 @@
         </row>
         <row r="134">
           <cell r="C134">
-            <v>7128.2073067128322</v>
+            <v>7182.9667332657464</v>
           </cell>
           <cell r="D134">
             <v>715.66165204613731</v>
           </cell>
           <cell r="E134">
-            <v>312</v>
+            <v>257.24057344708592</v>
           </cell>
           <cell r="F134">
             <v>131.96190102391498</v>
@@ -388,13 +1478,13 @@
         </row>
         <row r="135">
           <cell r="C135">
-            <v>7237.0218493461707</v>
+            <v>7268.1562775932571</v>
           </cell>
           <cell r="D135">
             <v>701.34841900521451</v>
           </cell>
           <cell r="E135">
-            <v>336.33333333333331</v>
+            <v>305.19890508624633</v>
           </cell>
           <cell r="F135">
             <v>143.65232192715405</v>
@@ -405,13 +1495,13 @@
         </row>
         <row r="136">
           <cell r="C136">
-            <v>7344.5890117015188</v>
+            <v>7352.2797613460125</v>
           </cell>
           <cell r="D136">
             <v>687.32145062511029</v>
           </cell>
           <cell r="E136">
-            <v>360.66666666666669</v>
+            <v>352.97591702217233</v>
           </cell>
           <cell r="F136">
             <v>155.53185910578233</v>
@@ -473,13 +1563,13 @@
         </row>
         <row r="140">
           <cell r="C140">
-            <v>7653.6409521142259</v>
+            <v>7678.866568796373</v>
           </cell>
           <cell r="D140">
             <v>633.96342174161373</v>
           </cell>
           <cell r="E140">
-            <v>458</v>
+            <v>432.77438331785265</v>
           </cell>
           <cell r="F140">
             <v>204.86717264669176</v>
@@ -490,13 +1580,13 @@
         </row>
         <row r="141">
           <cell r="C141">
-            <v>7700.7884783565314</v>
+            <v>7758.2240682276388</v>
           </cell>
           <cell r="D141">
             <v>621.28415330678149</v>
           </cell>
           <cell r="E141">
-            <v>482.33333333333331</v>
+            <v>424.89774346222532</v>
           </cell>
           <cell r="F141">
             <v>217.63714178303201</v>
@@ -507,13 +1597,13 @@
         </row>
         <row r="142">
           <cell r="C142">
-            <v>7746.9151429411868</v>
+            <v>7836.7406616153439</v>
           </cell>
           <cell r="D142">
             <v>608.85847024064583</v>
           </cell>
           <cell r="E142">
-            <v>506.66666666666669</v>
+            <v>416.84114799250932</v>
           </cell>
           <cell r="F142">
             <v>230.57444471910122</v>
@@ -524,13 +1614,13 @@
         </row>
         <row r="143">
           <cell r="C143">
-            <v>7792.0585525764764</v>
+            <v>7914.4536377888144</v>
           </cell>
           <cell r="D143">
             <v>596.68130083583287</v>
           </cell>
           <cell r="E143">
-            <v>531</v>
+            <v>408.60491478766164</v>
           </cell>
           <cell r="F143">
             <v>243.67558809182165</v>
@@ -541,13 +1631,13 @@
         </row>
         <row r="144">
           <cell r="C144">
-            <v>7836.2562994049604</v>
+            <v>7991.4002463658671</v>
           </cell>
           <cell r="D144">
             <v>584.74767481911624</v>
           </cell>
           <cell r="E144">
-            <v>555.33333333333337</v>
+            <v>400.18938637242582</v>
           </cell>
           <cell r="F144">
             <v>256.93711679228062</v>
@@ -558,13 +1648,13 @@
         </row>
         <row r="145">
           <cell r="C145">
-            <v>7879.5459713646242</v>
+            <v>8067.6177085596555</v>
           </cell>
           <cell r="D145">
             <v>573.05272132273387</v>
           </cell>
           <cell r="E145">
-            <v>579.66666666666663</v>
+            <v>391.59492947163466</v>
           </cell>
           <cell r="F145">
             <v>270.35561363300349</v>
@@ -575,13 +1665,13 @@
         </row>
         <row r="146">
           <cell r="C146">
-            <v>7921.9651626184632</v>
+            <v>8143.1432280487788</v>
           </cell>
           <cell r="D146">
             <v>561.59166689627921</v>
           </cell>
           <cell r="E146">
-            <v>604</v>
+            <v>382.82193456968452</v>
           </cell>
           <cell r="F146">
             <v>283.92769901778536</v>
@@ -592,13 +1682,13 @@
         </row>
         <row r="147">
           <cell r="C147">
-            <v>7963.5514840560863</v>
+            <v>8218.0140019142891</v>
           </cell>
           <cell r="D147">
             <v>550.35983355835356</v>
           </cell>
           <cell r="E147">
-            <v>628.33333333333337</v>
+            <v>373.8708154751302</v>
           </cell>
           <cell r="F147">
             <v>297.65003061406253</v>
@@ -609,13 +1699,13 @@
         </row>
         <row r="148">
           <cell r="C148">
-            <v>8004.3425738709338</v>
+            <v>8292.2672316472472</v>
           </cell>
           <cell r="D148">
             <v>539.35263688718646</v>
           </cell>
           <cell r="E148">
-            <v>652.66666666666663</v>
+            <v>364.74200889035319</v>
           </cell>
           <cell r="F148">
             <v>311.51930302780704</v>
@@ -626,13 +1716,13 @@
         </row>
         <row r="149">
           <cell r="C149">
-            <v>8044.3761082167875</v>
+            <v>8365.9401342305337</v>
           </cell>
           <cell r="D149">
             <v>528.56558414944266</v>
           </cell>
           <cell r="E149">
-            <v>677</v>
+            <v>355.43597398625434</v>
           </cell>
           <cell r="F149">
             <v>325.53224748092481</v>
@@ -643,13 +1733,13 @@
         </row>
         <row r="150">
           <cell r="C150">
-            <v>8083.6898119472444</v>
+            <v>8439.0699532986546</v>
           </cell>
           <cell r="D150">
             <v>517.99427246645382</v>
           </cell>
           <cell r="E150">
-            <v>701.33333333333337</v>
+            <v>345.9531919819234</v>
           </cell>
           <cell r="F150">
             <v>339.68563149114044</v>
@@ -660,13 +1750,13 @@
         </row>
         <row r="151">
           <cell r="C151">
-            <v>8122.3214694418766</v>
+            <v>8511.6939703793068</v>
           </cell>
           <cell r="D151">
             <v>507.63438701712477</v>
           </cell>
           <cell r="E151">
-            <v>725.66666666666663</v>
+            <v>336.29416572923748</v>
           </cell>
           <cell r="F151">
             <v>353.97625855435058</v>
@@ -677,13 +1767,13 @@
         </row>
         <row r="152">
           <cell r="C152">
-            <v>8160.3089355228558</v>
+            <v>8583.8495162205127</v>
           </cell>
           <cell r="D152">
             <v>497.48169927678225</v>
           </cell>
           <cell r="E152">
-            <v>750</v>
+            <v>326.45941930234289</v>
           </cell>
           <cell r="F152">
             <v>368.40096782942845</v>
@@ -694,13 +1784,13 @@
         </row>
         <row r="153">
           <cell r="C153">
-            <v>6039.6921628399505</v>
+            <v>6059.6921628399505</v>
           </cell>
           <cell r="D153">
             <v>912</v>
           </cell>
           <cell r="E153">
-            <v>20</v>
+            <v>0</v>
           </cell>
           <cell r="F153">
             <v>7.8422197749500002</v>
@@ -711,13 +1801,13 @@
         </row>
         <row r="154">
           <cell r="C154">
-            <v>6120.0692065962767</v>
+            <v>6164.4025399296097</v>
           </cell>
           <cell r="D154">
             <v>893.76</v>
           </cell>
           <cell r="E154">
-            <v>44.333333333333329</v>
+            <v>0</v>
           </cell>
           <cell r="F154">
             <v>8.6110502226513645</v>
@@ -728,13 +1818,13 @@
         </row>
         <row r="155">
           <cell r="C155">
-            <v>6198.9553648044894</v>
+            <v>6267.6220314711563</v>
           </cell>
           <cell r="D155">
             <v>875.88479999999993</v>
           </cell>
           <cell r="E155">
-            <v>68.666666666666657</v>
+            <v>0</v>
           </cell>
           <cell r="F155">
             <v>9.3961504441431867</v>
@@ -745,13 +1835,13 @@
         </row>
         <row r="156">
           <cell r="C156">
-            <v>6276.3862816116016</v>
+            <v>6369.3862816116016</v>
           </cell>
           <cell r="D156">
             <v>858.36710399999993</v>
           </cell>
           <cell r="E156">
-            <v>93</v>
+            <v>0</v>
           </cell>
           <cell r="F156">
             <v>10.197217750257561</v>
@@ -762,13 +1852,13 @@
         </row>
         <row r="157">
           <cell r="C157">
-            <v>6352.3974493617143</v>
+            <v>6469.7307826950473</v>
           </cell>
           <cell r="D157">
             <v>841.1997619199999</v>
           </cell>
           <cell r="E157">
-            <v>117.33333333333333</v>
+            <v>0</v>
           </cell>
           <cell r="F157">
             <v>11.013952675827259</v>
@@ -779,13 +1869,13 @@
         </row>
         <row r="158">
           <cell r="C158">
-            <v>6427.0242179530005</v>
+            <v>6568.6908846196675</v>
           </cell>
           <cell r="D158">
             <v>824.37576668159988</v>
           </cell>
           <cell r="E158">
-            <v>141.66666666666669</v>
+            <v>0</v>
           </cell>
           <cell r="F158">
             <v>11.846058951993687</v>
@@ -796,13 +1886,13 @@
         </row>
         <row r="159">
           <cell r="C159">
-            <v>6500.3018042056065</v>
+            <v>6666.3018042056065</v>
           </cell>
           <cell r="D159">
             <v>807.88825134796787</v>
           </cell>
           <cell r="E159">
-            <v>166</v>
+            <v>0</v>
           </cell>
           <cell r="F159">
             <v>12.693243478726256</v>
@@ -813,13 +1903,13 @@
         </row>
         <row r="160">
           <cell r="C160">
-            <v>6578.4103326319082</v>
+            <v>6768.7436659652412</v>
           </cell>
           <cell r="D160">
             <v>791.73048632100847</v>
           </cell>
           <cell r="E160">
-            <v>190.33333333333334</v>
+            <v>0</v>
           </cell>
           <cell r="F160">
             <v>7.4101849093282492</v>
@@ -830,13 +1920,13 @@
         </row>
         <row r="161">
           <cell r="C161">
-            <v>6649.3958430135181</v>
+            <v>6864.062509680185</v>
           </cell>
           <cell r="D161">
             <v>775.89587659458823</v>
           </cell>
           <cell r="E161">
-            <v>214.66666666666666</v>
+            <v>0</v>
           </cell>
           <cell r="F161">
             <v>7.9855354456854011</v>
@@ -847,13 +1937,13 @@
         </row>
         <row r="162">
           <cell r="C162">
-            <v>6719.1316864195223</v>
+            <v>6958.1316864195223</v>
           </cell>
           <cell r="D162">
             <v>760.3779590626965</v>
           </cell>
           <cell r="E162">
-            <v>239</v>
+            <v>0</v>
           </cell>
           <cell r="F162">
             <v>8.5805342129963194</v>
@@ -864,13 +1954,13 @@
         </row>
         <row r="163">
           <cell r="C163">
-            <v>6787.6522353787177</v>
+            <v>7050.9855687120507</v>
           </cell>
           <cell r="D163">
             <v>745.17039988144245</v>
           </cell>
           <cell r="E163">
-            <v>263.33333333333337</v>
+            <v>0</v>
           </cell>
           <cell r="F163">
             <v>9.195306504398939</v>
@@ -881,13 +1971,13 @@
         </row>
         <row r="164">
           <cell r="C164">
-            <v>6854.9917852369981</v>
+            <v>7142.6584519036651</v>
           </cell>
           <cell r="D164">
             <v>730.2669918838136</v>
           </cell>
           <cell r="E164">
-            <v>287.66666666666669</v>
+            <v>0</v>
           </cell>
           <cell r="F164">
             <v>9.8299718676271439</v>
@@ -898,13 +1988,13 @@
         </row>
         <row r="165">
           <cell r="C165">
-            <v>6921.1845635458058</v>
+            <v>7233.1845635458058</v>
           </cell>
           <cell r="D165">
             <v>715.66165204613731</v>
           </cell>
           <cell r="E165">
-            <v>312</v>
+            <v>0</v>
           </cell>
           <cell r="F165">
             <v>10.484644190941186</v>
@@ -915,13 +2005,13 @@
         </row>
         <row r="166">
           <cell r="C166">
-            <v>6986.2647394851974</v>
+            <v>7322.5980728185305</v>
           </cell>
           <cell r="D166">
             <v>701.34841900521451</v>
           </cell>
           <cell r="E166">
-            <v>336.33333333333331</v>
+            <v>0</v>
           </cell>
           <cell r="F166">
             <v>11.159431788126373</v>
@@ -932,13 +2022,13 @@
         </row>
         <row r="167">
           <cell r="C167">
-            <v>7050.2664333247303</v>
+            <v>7410.9330999913973</v>
           </cell>
           <cell r="D167">
             <v>687.32145062511029</v>
           </cell>
           <cell r="E167">
-            <v>360.66666666666669</v>
+            <v>0</v>
           </cell>
           <cell r="F167">
             <v>11.854437482568521</v>
@@ -949,13 +2039,13 @@
         </row>
         <row r="168">
           <cell r="C168">
-            <v>7113.2237259254916</v>
+            <v>7498.2237259254916</v>
           </cell>
           <cell r="D168">
             <v>673.575021612608</v>
           </cell>
           <cell r="E168">
-            <v>385</v>
+            <v>0</v>
           </cell>
           <cell r="F168">
             <v>12.569758690414773</v>
@@ -966,13 +2056,13 @@
         </row>
         <row r="169">
           <cell r="C169">
-            <v>7175.1706682865606</v>
+            <v>7584.5040016198936</v>
           </cell>
           <cell r="D169">
             <v>660.10352118035587</v>
           </cell>
           <cell r="E169">
-            <v>409.33333333333331</v>
+            <v>0</v>
           </cell>
           <cell r="F169">
             <v>13.305487502828036</v>
@@ -983,13 +2073,13 @@
         </row>
         <row r="170">
           <cell r="C170">
-            <v>7236.1412911392736</v>
+            <v>7669.8079578059405</v>
           </cell>
           <cell r="D170">
             <v>646.90145075674877</v>
           </cell>
           <cell r="E170">
-            <v>433.66666666666669</v>
+            <v>0</v>
           </cell>
           <cell r="F170">
             <v>14.061710767343449</v>
@@ -1000,13 +2090,13 @@
         </row>
         <row r="171">
           <cell r="C171">
-            <v>7296.1696145925835</v>
+            <v>7754.1696145925835</v>
           </cell>
           <cell r="D171">
             <v>633.96342174161373</v>
           </cell>
           <cell r="E171">
-            <v>458</v>
+            <v>0</v>
           </cell>
           <cell r="F171">
             <v>14.838510168335148</v>
@@ -1017,13 +2107,13 @@
         </row>
         <row r="172">
           <cell r="C172">
-            <v>7355.289657832961</v>
+            <v>7837.622991166294</v>
           </cell>
           <cell r="D172">
             <v>621.28415330678149</v>
           </cell>
           <cell r="E172">
-            <v>482.33333333333331</v>
+            <v>0</v>
           </cell>
           <cell r="F172">
             <v>15.635962306601458</v>
@@ -1034,13 +2124,13 @@
         </row>
         <row r="173">
           <cell r="C173">
-            <v>7413.5354488822113</v>
+            <v>7920.2021155488783</v>
           </cell>
           <cell r="D173">
             <v>608.85847024064583</v>
           </cell>
           <cell r="E173">
-            <v>506.66666666666669</v>
+            <v>0</v>
           </cell>
           <cell r="F173">
             <v>16.454138778076707</v>
@@ -1051,13 +2141,13 @@
         </row>
         <row r="174">
           <cell r="C174">
-            <v>7470.9410344166208</v>
+            <v>8001.9410344166208</v>
           </cell>
           <cell r="D174">
             <v>596.68130083583287</v>
           </cell>
           <cell r="E174">
-            <v>531</v>
+            <v>0</v>
           </cell>
           <cell r="F174">
             <v>17.293106251677663</v>
@@ -1068,13 +2158,13 @@
         </row>
         <row r="175">
           <cell r="C175">
-            <v>7527.5404896509481</v>
+            <v>8082.8738229842811</v>
           </cell>
           <cell r="D175">
             <v>584.74767481911624</v>
           </cell>
           <cell r="E175">
-            <v>555.33333333333337</v>
+            <v>0</v>
           </cell>
           <cell r="F175">
             <v>18.152926546292662</v>
@@ -1085,13 +2175,13 @@
         </row>
         <row r="176">
           <cell r="C176">
-            <v>7583.3679282907042</v>
+            <v>8163.0345949573712</v>
           </cell>
           <cell r="D176">
             <v>573.05272132273387</v>
           </cell>
           <cell r="E176">
-            <v>579.66666666666663</v>
+            <v>0</v>
           </cell>
           <cell r="F176">
             <v>19.033656706921217</v>
@@ -1102,13 +2192,13 @@
         </row>
         <row r="177">
           <cell r="C177">
-            <v>7638.457512556276</v>
+            <v>8242.4575125562769</v>
           </cell>
           <cell r="D177">
             <v>561.59166689627921</v>
           </cell>
           <cell r="E177">
-            <v>604</v>
+            <v>0</v>
           </cell>
           <cell r="F177">
             <v>19.935349079972163</v>
@@ -1119,13 +2209,13 @@
         </row>
         <row r="178">
           <cell r="C178">
-            <v>7692.8434632824201</v>
+            <v>8321.1767966157531</v>
           </cell>
           <cell r="D178">
             <v>550.35983355835356</v>
           </cell>
           <cell r="E178">
-            <v>628.33333333333337</v>
+            <v>0</v>
           </cell>
           <cell r="F178">
             <v>20.858051387727865</v>
@@ -1136,13 +2226,13 @@
         </row>
         <row r="179">
           <cell r="C179">
-            <v>7746.5600700967589</v>
+            <v>8399.2267367634267</v>
           </cell>
           <cell r="D179">
             <v>539.35263688718646</v>
           </cell>
           <cell r="E179">
-            <v>652.66666666666663</v>
+            <v>0</v>
           </cell>
           <cell r="F179">
             <v>21.801806801982551</v>
@@ -1153,13 +2243,13 @@
         </row>
         <row r="180">
           <cell r="C180">
-            <v>7799.6417016808518</v>
+            <v>8476.64170168085</v>
           </cell>
           <cell r="D180">
             <v>528.56558414944266</v>
           </cell>
           <cell r="E180">
-            <v>677</v>
+            <v>0</v>
           </cell>
           <cell r="F180">
             <v>22.766654016862141</v>
@@ -1170,13 +2260,13 @@
         </row>
         <row r="181">
           <cell r="C181">
-            <v>7852.1228161175522</v>
+            <v>8553.4561494508853</v>
           </cell>
           <cell r="D181">
             <v>517.99427246645382</v>
           </cell>
           <cell r="E181">
-            <v>701.33333333333337</v>
+            <v>0</v>
           </cell>
           <cell r="F181">
             <v>23.752627320833305</v>
@@ -1187,13 +2277,13 @@
         </row>
         <row r="182">
           <cell r="C182">
-            <v>7904.0379713283182</v>
+            <v>8629.7046379949861</v>
           </cell>
           <cell r="D182">
             <v>507.63438701712477</v>
           </cell>
           <cell r="E182">
-            <v>725.66666666666663</v>
+            <v>0</v>
           </cell>
           <cell r="F182">
             <v>24.759756667909301</v>
@@ -1204,1073 +2294,19 @@
         </row>
         <row r="183">
           <cell r="C183">
-            <v>7955.4218356042229</v>
+            <v>8705.421835604222</v>
           </cell>
           <cell r="D183">
             <v>497.48169927678225</v>
           </cell>
           <cell r="E183">
-            <v>750</v>
+            <v>0</v>
           </cell>
           <cell r="F183">
             <v>25.788067748059987</v>
           </cell>
           <cell r="G183">
             <v>44.382022403296808</v>
-          </cell>
-        </row>
-        <row r="202">
-          <cell r="C202">
-            <v>784.22197749500003</v>
-          </cell>
-          <cell r="D202">
-            <v>389.62701858989999</v>
-          </cell>
-          <cell r="E202">
-            <v>5865.68538653</v>
-          </cell>
-          <cell r="F202">
-            <v>0</v>
-          </cell>
-          <cell r="G202">
-            <v>7039.5343826149001</v>
-          </cell>
-        </row>
-        <row r="203">
-          <cell r="C203">
-            <v>794.86617439858742</v>
-          </cell>
-          <cell r="D203">
-            <v>403.93296803511453</v>
-          </cell>
-          <cell r="E203">
-            <v>5927.3744477185592</v>
-          </cell>
-          <cell r="F203">
-            <v>0</v>
-          </cell>
-          <cell r="G203">
-            <v>7126.1735901522607</v>
-          </cell>
-        </row>
-        <row r="204">
-          <cell r="C204">
-            <v>805.38432378370169</v>
-          </cell>
-          <cell r="D204">
-            <v>418.62357806823337</v>
-          </cell>
-          <cell r="E204">
-            <v>5987.7010800633643</v>
-          </cell>
-          <cell r="F204">
-            <v>0</v>
-          </cell>
-          <cell r="G204">
-            <v>7211.7089819152989</v>
-          </cell>
-        </row>
-        <row r="205">
-          <cell r="C205">
-            <v>815.77742002060484</v>
-          </cell>
-          <cell r="D205">
-            <v>433.70798901525569</v>
-          </cell>
-          <cell r="E205">
-            <v>6046.6831343259983</v>
-          </cell>
-          <cell r="F205">
-            <v>0</v>
-          </cell>
-          <cell r="G205">
-            <v>7296.1685433618586</v>
-          </cell>
-        </row>
-        <row r="206">
-          <cell r="C206">
-            <v>826.0464506870444</v>
-          </cell>
-          <cell r="D206">
-            <v>449.19554435252496</v>
-          </cell>
-          <cell r="E206">
-            <v>6104.3382628513064</v>
-          </cell>
-          <cell r="F206">
-            <v>0</v>
-          </cell>
-          <cell r="G206">
-            <v>7379.5802578908751</v>
-          </cell>
-        </row>
-        <row r="207">
-          <cell r="C207">
-            <v>836.19239661131905</v>
-          </cell>
-          <cell r="D207">
-            <v>465.09579503632892</v>
-          </cell>
-          <cell r="E207">
-            <v>6160.6839215996133</v>
-          </cell>
-          <cell r="F207">
-            <v>0</v>
-          </cell>
-          <cell r="G207">
-            <v>7461.9721132472614</v>
-          </cell>
-        </row>
-        <row r="208">
-          <cell r="C208">
-            <v>846.21623191508377</v>
-          </cell>
-          <cell r="D208">
-            <v>481.41850392215304</v>
-          </cell>
-          <cell r="E208">
-            <v>6215.737372159123</v>
-          </cell>
-          <cell r="F208">
-            <v>0</v>
-          </cell>
-          <cell r="G208">
-            <v>7543.3721079963598</v>
-          </cell>
-        </row>
-        <row r="209">
-          <cell r="C209">
-            <v>856.11892405589538</v>
-          </cell>
-          <cell r="D209">
-            <v>498.17365027540257</v>
-          </cell>
-          <cell r="E209">
-            <v>6269.5156837386994</v>
-          </cell>
-          <cell r="F209">
-            <v>54.75</v>
-          </cell>
-          <cell r="G209">
-            <v>7678.5582580699975</v>
-          </cell>
-        </row>
-        <row r="210">
-          <cell r="C210">
-            <v>865.90143386950137</v>
-          </cell>
-          <cell r="D210">
-            <v>515.37143437544944</v>
-          </cell>
-          <cell r="E210">
-            <v>6322.035735141184</v>
-          </cell>
-          <cell r="F210">
-            <v>109.5</v>
-          </cell>
-          <cell r="G210">
-            <v>7812.8086033861346</v>
-          </cell>
-        </row>
-        <row r="211">
-          <cell r="C211">
-            <v>875.56471561186947</v>
-          </cell>
-          <cell r="D211">
-            <v>533.02228221489327</v>
-          </cell>
-          <cell r="E211">
-            <v>6373.3142167174701</v>
-          </cell>
-          <cell r="F211">
-            <v>164.25</v>
-          </cell>
-          <cell r="G211">
-            <v>7946.151214544233</v>
-          </cell>
-        </row>
-        <row r="212">
-          <cell r="C212">
-            <v>885.10971700096752</v>
-          </cell>
-          <cell r="D212">
-            <v>551.13685029596729</v>
-          </cell>
-          <cell r="E212">
-            <v>6423.3676323014861</v>
-          </cell>
-          <cell r="F212">
-            <v>219</v>
-          </cell>
-          <cell r="G212">
-            <v>8078.6141995984208</v>
-          </cell>
-        </row>
-        <row r="213">
-          <cell r="C213">
-            <v>894.53737925828398</v>
-          </cell>
-          <cell r="D213">
-            <v>569.72603052605507</v>
-          </cell>
-          <cell r="E213">
-            <v>6472.2123011262884</v>
-          </cell>
-          <cell r="F213">
-            <v>273.75</v>
-          </cell>
-          <cell r="G213">
-            <v>8210.2257109106285</v>
-          </cell>
-        </row>
-        <row r="214">
-          <cell r="C214">
-            <v>903.84863715010238</v>
-          </cell>
-          <cell r="D214">
-            <v>588.80095521432304</v>
-          </cell>
-          <cell r="E214">
-            <v>6519.8643597214268</v>
-          </cell>
-          <cell r="F214">
-            <v>328.5</v>
-          </cell>
-          <cell r="G214">
-            <v>8341.013952085852</v>
-          </cell>
-        </row>
-        <row r="215">
-          <cell r="C215">
-            <v>913.04441902852136</v>
-          </cell>
-          <cell r="D215">
-            <v>608.3730021715196</v>
-          </cell>
-          <cell r="E215">
-            <v>6566.3397637917687</v>
-          </cell>
-          <cell r="F215">
-            <v>383.25</v>
-          </cell>
-          <cell r="G215">
-            <v>8471.0071849918095</v>
-          </cell>
-        </row>
-        <row r="216">
-          <cell r="C216">
-            <v>922.12564687222732</v>
-          </cell>
-          <cell r="D216">
-            <v>628.45379991502341</v>
-          </cell>
-          <cell r="E216">
-            <v>6611.654290077965</v>
-          </cell>
-          <cell r="F216">
-            <v>438</v>
-          </cell>
-          <cell r="G216">
-            <v>8600.2337368652152</v>
-          </cell>
-        </row>
-        <row r="217">
-          <cell r="C217">
-            <v>931.09323632702035</v>
-          </cell>
-          <cell r="D217">
-            <v>649.05523298127218</v>
-          </cell>
-          <cell r="E217">
-            <v>6655.8235381986988</v>
-          </cell>
-          <cell r="F217">
-            <v>492.75</v>
-          </cell>
-          <cell r="G217">
-            <v>8728.7220075069908</v>
-          </cell>
-        </row>
-        <row r="218">
-          <cell r="C218">
-            <v>939.9480967460936</v>
-          </cell>
-          <cell r="D218">
-            <v>670.18944734774129</v>
-          </cell>
-          <cell r="E218">
-            <v>6698.8629324749354</v>
-          </cell>
-          <cell r="F218">
-            <v>547.5</v>
-          </cell>
-          <cell r="G218">
-            <v>8856.50047656877</v>
-          </cell>
-        </row>
-        <row r="219">
-          <cell r="C219">
-            <v>948.69113123006798</v>
-          </cell>
-          <cell r="D219">
-            <v>691.86885596669049</v>
-          </cell>
-          <cell r="E219">
-            <v>6740.7877237363109</v>
-          </cell>
-          <cell r="F219">
-            <v>547.5</v>
-          </cell>
-          <cell r="G219">
-            <v>8928.8477109330688</v>
-          </cell>
-        </row>
-        <row r="220">
-          <cell r="C220">
-            <v>957.32323666678394</v>
-          </cell>
-          <cell r="D220">
-            <v>714.10614441293103</v>
-          </cell>
-          <cell r="E220">
-            <v>6781.6129911098215</v>
-          </cell>
-          <cell r="F220">
-            <v>547.5</v>
-          </cell>
-          <cell r="G220">
-            <v>9000.5423721895368</v>
-          </cell>
-        </row>
-        <row r="221">
-          <cell r="C221">
-            <v>965.84530377085218</v>
-          </cell>
-          <cell r="D221">
-            <v>736.91427664792297</v>
-          </cell>
-          <cell r="E221">
-            <v>6821.353643791037</v>
-          </cell>
-          <cell r="F221">
-            <v>547.5</v>
-          </cell>
-          <cell r="G221">
-            <v>9071.613224209812</v>
-          </cell>
-        </row>
-        <row r="222">
-          <cell r="C222">
-            <v>974.25821712296306</v>
-          </cell>
-          <cell r="D222">
-            <v>760.30650090254744</v>
-          </cell>
-          <cell r="E222">
-            <v>6860.0244227979247</v>
-          </cell>
-          <cell r="F222">
-            <v>547.5</v>
-          </cell>
-          <cell r="G222">
-            <v>9142.0891408234347</v>
-          </cell>
-        </row>
-        <row r="223">
-          <cell r="C223">
-            <v>982.56285520895824</v>
-          </cell>
-          <cell r="D223">
-            <v>784.29635568095091</v>
-          </cell>
-          <cell r="E223">
-            <v>6897.6399027074976</v>
-          </cell>
-          <cell r="F223">
-            <v>547.5</v>
-          </cell>
-          <cell r="G223">
-            <v>9211.9991135974069</v>
-          </cell>
-        </row>
-        <row r="224">
-          <cell r="C224">
-            <v>990.76009045866579</v>
-          </cell>
-          <cell r="D224">
-            <v>808.89767588790824</v>
-          </cell>
-          <cell r="E224">
-            <v>6934.2144933754589</v>
-          </cell>
-          <cell r="F224">
-            <v>547.5</v>
-          </cell>
-          <cell r="G224">
-            <v>9281.372259722033</v>
-          </cell>
-        </row>
-        <row r="225">
-          <cell r="C225">
-            <v>998.8507892844957</v>
-          </cell>
-          <cell r="D225">
-            <v>834.12459908219046</v>
-          </cell>
-          <cell r="E225">
-            <v>6969.7624416389599</v>
-          </cell>
-          <cell r="F225">
-            <v>547.5</v>
-          </cell>
-          <cell r="G225">
-            <v>9350.2378300056462</v>
-          </cell>
-        </row>
-        <row r="226">
-          <cell r="C226">
-            <v>1006.8358121198061</v>
-          </cell>
-          <cell r="D226">
-            <v>859.99157185848537</v>
-          </cell>
-          <cell r="E226">
-            <v>7004.2978330026699</v>
-          </cell>
-          <cell r="F226">
-            <v>547.5</v>
-          </cell>
-          <cell r="G226">
-            <v>9418.6252169809613</v>
-          </cell>
-        </row>
-        <row r="227">
-          <cell r="C227">
-            <v>1014.7160134570314</v>
-          </cell>
-          <cell r="D227">
-            <v>886.51335636045974</v>
-          </cell>
-          <cell r="E227">
-            <v>7037.8345933082928</v>
-          </cell>
-          <cell r="F227">
-            <v>547.5</v>
-          </cell>
-          <cell r="G227">
-            <v>9486.5639631257836</v>
-          </cell>
-        </row>
-        <row r="228">
-          <cell r="C228">
-            <v>1022.4922418855811</v>
-          </cell>
-          <cell r="D228">
-            <v>913.7050369276069</v>
-          </cell>
-          <cell r="E228">
-            <v>7070.3864903877156</v>
-          </cell>
-          <cell r="F228">
-            <v>547.5</v>
-          </cell>
-          <cell r="G228">
-            <v>9554.0837692009045</v>
-          </cell>
-        </row>
-        <row r="229">
-          <cell r="C229">
-            <v>1030.1653401295089</v>
-          </cell>
-          <cell r="D229">
-            <v>941.58202687857829</v>
-          </cell>
-          <cell r="E229">
-            <v>7101.9671356998942</v>
-          </cell>
-          <cell r="F229">
-            <v>547.5</v>
-          </cell>
-          <cell r="G229">
-            <v>9621.2145027079823</v>
-          </cell>
-        </row>
-        <row r="230">
-          <cell r="C230">
-            <v>1037.7361450849505</v>
-          </cell>
-          <cell r="D230">
-            <v>970.16007543374485</v>
-          </cell>
-          <cell r="E230">
-            <v>7132.5899859516949</v>
-          </cell>
-          <cell r="F230">
-            <v>547.5</v>
-          </cell>
-          <cell r="G230">
-            <v>9687.9862064703902</v>
-          </cell>
-        </row>
-        <row r="231">
-          <cell r="C231">
-            <v>1045.2054878573344</v>
-          </cell>
-          <cell r="D231">
-            <v>999.45527477979738</v>
-          </cell>
-          <cell r="E231">
-            <v>7162.268344702783</v>
-          </cell>
-          <cell r="F231">
-            <v>547.5</v>
-          </cell>
-          <cell r="G231">
-            <v>9754.4291073399145</v>
-          </cell>
-        </row>
-        <row r="232">
-          <cell r="C232">
-            <v>1052.5741937983671</v>
-          </cell>
-          <cell r="D232">
-            <v>1029.4840672792445</v>
-          </cell>
-          <cell r="E232">
-            <v>7191.0153639547507</v>
-          </cell>
-          <cell r="F232">
-            <v>547.5</v>
-          </cell>
-          <cell r="G232">
-            <v>9820.5736250323625</v>
-          </cell>
-        </row>
-        <row r="233">
-          <cell r="C233">
-            <v>784.22197749500003</v>
-          </cell>
-          <cell r="D233">
-            <v>389.62701858989999</v>
-          </cell>
-          <cell r="E233">
-            <v>5865.68538653</v>
-          </cell>
-          <cell r="F233">
-            <v>0</v>
-          </cell>
-          <cell r="G233">
-            <v>7039.5343826149001</v>
-          </cell>
-        </row>
-        <row r="234">
-          <cell r="C234">
-            <v>794.86617439858742</v>
-          </cell>
-          <cell r="D234">
-            <v>403.93296803511453</v>
-          </cell>
-          <cell r="E234">
-            <v>5927.3744477185592</v>
-          </cell>
-          <cell r="F234">
-            <v>0</v>
-          </cell>
-          <cell r="G234">
-            <v>7126.1735901522607</v>
-          </cell>
-        </row>
-        <row r="235">
-          <cell r="C235">
-            <v>805.38432378370169</v>
-          </cell>
-          <cell r="D235">
-            <v>418.62357806823337</v>
-          </cell>
-          <cell r="E235">
-            <v>5987.7010800633643</v>
-          </cell>
-          <cell r="F235">
-            <v>0</v>
-          </cell>
-          <cell r="G235">
-            <v>7211.7089819152989</v>
-          </cell>
-        </row>
-        <row r="236">
-          <cell r="C236">
-            <v>815.77742002060484</v>
-          </cell>
-          <cell r="D236">
-            <v>433.70798901525569</v>
-          </cell>
-          <cell r="E236">
-            <v>6046.6831343259983</v>
-          </cell>
-          <cell r="F236">
-            <v>0</v>
-          </cell>
-          <cell r="G236">
-            <v>7296.1685433618586</v>
-          </cell>
-        </row>
-        <row r="237">
-          <cell r="C237">
-            <v>826.0464506870444</v>
-          </cell>
-          <cell r="D237">
-            <v>449.19554435252496</v>
-          </cell>
-          <cell r="E237">
-            <v>6104.3382628513064</v>
-          </cell>
-          <cell r="F237">
-            <v>0</v>
-          </cell>
-          <cell r="G237">
-            <v>7379.5802578908751</v>
-          </cell>
-        </row>
-        <row r="238">
-          <cell r="C238">
-            <v>836.19239661131905</v>
-          </cell>
-          <cell r="D238">
-            <v>465.09579503632892</v>
-          </cell>
-          <cell r="E238">
-            <v>6160.6839215996133</v>
-          </cell>
-          <cell r="F238">
-            <v>0</v>
-          </cell>
-          <cell r="G238">
-            <v>7461.9721132472614</v>
-          </cell>
-        </row>
-        <row r="239">
-          <cell r="C239">
-            <v>846.21623191508377</v>
-          </cell>
-          <cell r="D239">
-            <v>481.41850392215304</v>
-          </cell>
-          <cell r="E239">
-            <v>6215.737372159123</v>
-          </cell>
-          <cell r="F239">
-            <v>0</v>
-          </cell>
-          <cell r="G239">
-            <v>7543.3721079963598</v>
-          </cell>
-        </row>
-        <row r="240">
-          <cell r="C240">
-            <v>856.11892405589538</v>
-          </cell>
-          <cell r="D240">
-            <v>498.17365027540257</v>
-          </cell>
-          <cell r="E240">
-            <v>6269.5156837386994</v>
-          </cell>
-          <cell r="F240">
-            <v>0</v>
-          </cell>
-          <cell r="G240">
-            <v>7623.8082580699975</v>
-          </cell>
-        </row>
-        <row r="241">
-          <cell r="C241">
-            <v>865.90143386950137</v>
-          </cell>
-          <cell r="D241">
-            <v>515.37143437544944</v>
-          </cell>
-          <cell r="E241">
-            <v>6322.035735141184</v>
-          </cell>
-          <cell r="F241">
-            <v>0</v>
-          </cell>
-          <cell r="G241">
-            <v>7703.3086033861346</v>
-          </cell>
-        </row>
-        <row r="242">
-          <cell r="C242">
-            <v>875.56471561186947</v>
-          </cell>
-          <cell r="D242">
-            <v>533.02228221489327</v>
-          </cell>
-          <cell r="E242">
-            <v>6373.3142167174701</v>
-          </cell>
-          <cell r="F242">
-            <v>0</v>
-          </cell>
-          <cell r="G242">
-            <v>7781.901214544233</v>
-          </cell>
-        </row>
-        <row r="243">
-          <cell r="C243">
-            <v>885.10971700096752</v>
-          </cell>
-          <cell r="D243">
-            <v>551.13685029596729</v>
-          </cell>
-          <cell r="E243">
-            <v>6423.3676323014861</v>
-          </cell>
-          <cell r="F243">
-            <v>0</v>
-          </cell>
-          <cell r="G243">
-            <v>7859.6141995984208</v>
-          </cell>
-        </row>
-        <row r="244">
-          <cell r="C244">
-            <v>894.53737925828398</v>
-          </cell>
-          <cell r="D244">
-            <v>569.72603052605507</v>
-          </cell>
-          <cell r="E244">
-            <v>6472.2123011262884</v>
-          </cell>
-          <cell r="F244">
-            <v>0</v>
-          </cell>
-          <cell r="G244">
-            <v>7936.4757109106276</v>
-          </cell>
-        </row>
-        <row r="245">
-          <cell r="C245">
-            <v>903.84863715010238</v>
-          </cell>
-          <cell r="D245">
-            <v>588.80095521432304</v>
-          </cell>
-          <cell r="E245">
-            <v>6519.8643597214268</v>
-          </cell>
-          <cell r="F245">
-            <v>0</v>
-          </cell>
-          <cell r="G245">
-            <v>8012.513952085852</v>
-          </cell>
-        </row>
-        <row r="246">
-          <cell r="C246">
-            <v>913.04441902852136</v>
-          </cell>
-          <cell r="D246">
-            <v>608.3730021715196</v>
-          </cell>
-          <cell r="E246">
-            <v>6566.3397637917687</v>
-          </cell>
-          <cell r="F246">
-            <v>0</v>
-          </cell>
-          <cell r="G246">
-            <v>8087.7571849918095</v>
-          </cell>
-        </row>
-        <row r="247">
-          <cell r="C247">
-            <v>922.12564687222732</v>
-          </cell>
-          <cell r="D247">
-            <v>628.45379991502341</v>
-          </cell>
-          <cell r="E247">
-            <v>6611.654290077965</v>
-          </cell>
-          <cell r="F247">
-            <v>0</v>
-          </cell>
-          <cell r="G247">
-            <v>8162.2337368652152</v>
-          </cell>
-        </row>
-        <row r="248">
-          <cell r="C248">
-            <v>931.09323632702035</v>
-          </cell>
-          <cell r="D248">
-            <v>649.05523298127218</v>
-          </cell>
-          <cell r="E248">
-            <v>6655.8235381986988</v>
-          </cell>
-          <cell r="F248">
-            <v>0</v>
-          </cell>
-          <cell r="G248">
-            <v>8235.9720075069908</v>
-          </cell>
-        </row>
-        <row r="249">
-          <cell r="C249">
-            <v>939.9480967460936</v>
-          </cell>
-          <cell r="D249">
-            <v>670.18944734774129</v>
-          </cell>
-          <cell r="E249">
-            <v>6698.8629324749354</v>
-          </cell>
-          <cell r="F249">
-            <v>0</v>
-          </cell>
-          <cell r="G249">
-            <v>8309.00047656877</v>
-          </cell>
-        </row>
-        <row r="250">
-          <cell r="C250">
-            <v>948.69113123006798</v>
-          </cell>
-          <cell r="D250">
-            <v>691.86885596669049</v>
-          </cell>
-          <cell r="E250">
-            <v>6740.7877237363109</v>
-          </cell>
-          <cell r="F250">
-            <v>0</v>
-          </cell>
-          <cell r="G250">
-            <v>8381.3477109330688</v>
-          </cell>
-        </row>
-        <row r="251">
-          <cell r="C251">
-            <v>957.32323666678394</v>
-          </cell>
-          <cell r="D251">
-            <v>714.10614441293103</v>
-          </cell>
-          <cell r="E251">
-            <v>6781.6129911098215</v>
-          </cell>
-          <cell r="F251">
-            <v>0</v>
-          </cell>
-          <cell r="G251">
-            <v>8453.0423721895368</v>
-          </cell>
-        </row>
-        <row r="252">
-          <cell r="C252">
-            <v>965.84530377085218</v>
-          </cell>
-          <cell r="D252">
-            <v>736.91427664792297</v>
-          </cell>
-          <cell r="E252">
-            <v>6821.353643791037</v>
-          </cell>
-          <cell r="F252">
-            <v>0</v>
-          </cell>
-          <cell r="G252">
-            <v>8524.113224209812</v>
-          </cell>
-        </row>
-        <row r="253">
-          <cell r="C253">
-            <v>974.25821712296306</v>
-          </cell>
-          <cell r="D253">
-            <v>760.30650090254744</v>
-          </cell>
-          <cell r="E253">
-            <v>6860.0244227979247</v>
-          </cell>
-          <cell r="F253">
-            <v>0</v>
-          </cell>
-          <cell r="G253">
-            <v>8594.5891408234347</v>
-          </cell>
-        </row>
-        <row r="254">
-          <cell r="C254">
-            <v>982.56285520895824</v>
-          </cell>
-          <cell r="D254">
-            <v>784.29635568095091</v>
-          </cell>
-          <cell r="E254">
-            <v>6897.6399027074976</v>
-          </cell>
-          <cell r="F254">
-            <v>0</v>
-          </cell>
-          <cell r="G254">
-            <v>8664.4991135974069</v>
-          </cell>
-        </row>
-        <row r="255">
-          <cell r="C255">
-            <v>990.76009045866579</v>
-          </cell>
-          <cell r="D255">
-            <v>808.89767588790824</v>
-          </cell>
-          <cell r="E255">
-            <v>6934.2144933754589</v>
-          </cell>
-          <cell r="F255">
-            <v>0</v>
-          </cell>
-          <cell r="G255">
-            <v>8733.872259722033</v>
-          </cell>
-        </row>
-        <row r="256">
-          <cell r="C256">
-            <v>998.8507892844957</v>
-          </cell>
-          <cell r="D256">
-            <v>834.12459908219046</v>
-          </cell>
-          <cell r="E256">
-            <v>6969.7624416389599</v>
-          </cell>
-          <cell r="F256">
-            <v>0</v>
-          </cell>
-          <cell r="G256">
-            <v>8802.7378300056462</v>
-          </cell>
-        </row>
-        <row r="257">
-          <cell r="C257">
-            <v>1006.8358121198061</v>
-          </cell>
-          <cell r="D257">
-            <v>859.99157185848537</v>
-          </cell>
-          <cell r="E257">
-            <v>7004.2978330026699</v>
-          </cell>
-          <cell r="F257">
-            <v>0</v>
-          </cell>
-          <cell r="G257">
-            <v>8871.1252169809613</v>
-          </cell>
-        </row>
-        <row r="258">
-          <cell r="C258">
-            <v>1014.7160134570314</v>
-          </cell>
-          <cell r="D258">
-            <v>886.51335636045974</v>
-          </cell>
-          <cell r="E258">
-            <v>7037.8345933082928</v>
-          </cell>
-          <cell r="F258">
-            <v>0</v>
-          </cell>
-          <cell r="G258">
-            <v>8939.0639631257836</v>
-          </cell>
-        </row>
-        <row r="259">
-          <cell r="C259">
-            <v>1022.4922418855811</v>
-          </cell>
-          <cell r="D259">
-            <v>913.7050369276069</v>
-          </cell>
-          <cell r="E259">
-            <v>7070.3864903877156</v>
-          </cell>
-          <cell r="F259">
-            <v>0</v>
-          </cell>
-          <cell r="G259">
-            <v>9006.5837692009045</v>
-          </cell>
-        </row>
-        <row r="260">
-          <cell r="C260">
-            <v>1030.1653401295089</v>
-          </cell>
-          <cell r="D260">
-            <v>941.58202687857829</v>
-          </cell>
-          <cell r="E260">
-            <v>7101.9671356998942</v>
-          </cell>
-          <cell r="F260">
-            <v>0</v>
-          </cell>
-          <cell r="G260">
-            <v>9073.7145027079823</v>
-          </cell>
-        </row>
-        <row r="261">
-          <cell r="C261">
-            <v>1037.7361450849505</v>
-          </cell>
-          <cell r="D261">
-            <v>970.16007543374485</v>
-          </cell>
-          <cell r="E261">
-            <v>7132.5899859516949</v>
-          </cell>
-          <cell r="F261">
-            <v>0</v>
-          </cell>
-          <cell r="G261">
-            <v>9140.4862064703902</v>
-          </cell>
-        </row>
-        <row r="262">
-          <cell r="C262">
-            <v>1045.2054878573344</v>
-          </cell>
-          <cell r="D262">
-            <v>999.45527477979738</v>
-          </cell>
-          <cell r="E262">
-            <v>7162.268344702783</v>
-          </cell>
-          <cell r="F262">
-            <v>0</v>
-          </cell>
-          <cell r="G262">
-            <v>9206.9291073399145</v>
-          </cell>
-        </row>
-        <row r="263">
-          <cell r="C263">
-            <v>1052.5741937983671</v>
-          </cell>
-          <cell r="D263">
-            <v>1029.4840672792445</v>
-          </cell>
-          <cell r="E263">
-            <v>7191.0153639547507</v>
-          </cell>
-          <cell r="F263">
-            <v>0</v>
-          </cell>
-          <cell r="G263">
-            <v>9273.0736250323625</v>
           </cell>
         </row>
       </sheetData>
@@ -2639,23 +2675,23 @@
         <v>2020</v>
       </c>
       <c r="B2" s="1">
-        <f>+[1]Summary!C122</f>
-        <v>6039.6921628399505</v>
+        <f>+[2]Summary!C122</f>
+        <v>6059.6921628399505</v>
       </c>
       <c r="C2" s="1">
-        <f>+[1]Summary!D122</f>
+        <f>+[2]Summary!D122</f>
         <v>912</v>
       </c>
       <c r="D2" s="1">
-        <f>+[1]Summary!E122</f>
-        <v>20</v>
+        <f>+[2]Summary!E122</f>
+        <v>0</v>
       </c>
       <c r="E2" s="1">
-        <f>+[1]Summary!F122</f>
+        <f>+[2]Summary!F122</f>
         <v>7.8422197749500002</v>
       </c>
       <c r="F2" s="1">
-        <f>+[1]Summary!G122</f>
+        <f>+[2]Summary!G122</f>
         <v>60</v>
       </c>
       <c r="G2" s="1">
@@ -2674,23 +2710,23 @@
         <v>2021</v>
       </c>
       <c r="B3" s="1">
-        <f>+[1]Summary!C123</f>
-        <v>6111.7231117650917</v>
+        <f>+[2]Summary!C123</f>
+        <v>6156.0564450984248</v>
       </c>
       <c r="C3" s="1">
-        <f>+[1]Summary!D123</f>
+        <f>+[2]Summary!D123</f>
         <v>893.76</v>
       </c>
       <c r="D3" s="1">
-        <f>+[1]Summary!E123</f>
-        <v>44.333333333333329</v>
+        <f>+[2]Summary!E123</f>
+        <v>0</v>
       </c>
       <c r="E3" s="1">
-        <f>+[1]Summary!F123</f>
+        <f>+[2]Summary!F123</f>
         <v>16.95714505383653</v>
       </c>
       <c r="F3" s="1">
-        <f>+[1]Summary!G123</f>
+        <f>+[2]Summary!G123</f>
         <v>59.4</v>
       </c>
       <c r="G3" s="1">
@@ -2709,23 +2745,23 @@
         <v>2022</v>
       </c>
       <c r="B4" s="1">
-        <f>+[1]Summary!C124</f>
-        <v>6182.0422940050321</v>
+        <f>+[2]Summary!C124</f>
+        <v>6250.7089606716991</v>
       </c>
       <c r="C4" s="1">
-        <f>+[1]Summary!D124</f>
+        <f>+[2]Summary!D124</f>
         <v>875.88479999999993</v>
       </c>
       <c r="D4" s="1">
-        <f>+[1]Summary!E124</f>
-        <v>68.666666666666657</v>
+        <f>+[2]Summary!E124</f>
+        <v>0</v>
       </c>
       <c r="E4" s="1">
-        <f>+[1]Summary!F124</f>
+        <f>+[2]Summary!F124</f>
         <v>26.30922124360092</v>
       </c>
       <c r="F4" s="1">
-        <f>+[1]Summary!G124</f>
+        <f>+[2]Summary!G124</f>
         <v>58.805999999999997</v>
       </c>
       <c r="G4" s="1">
@@ -2744,23 +2780,23 @@
         <v>2023</v>
       </c>
       <c r="B5" s="1">
-        <f>+[1]Summary!C125</f>
-        <v>6250.689292880953</v>
+        <f>+[2]Summary!C125</f>
+        <v>6343.689292880953</v>
       </c>
       <c r="C5" s="1">
-        <f>+[1]Summary!D125</f>
+        <f>+[2]Summary!D125</f>
         <v>858.36710399999993</v>
       </c>
       <c r="D5" s="1">
-        <f>+[1]Summary!E125</f>
-        <v>93</v>
+        <f>+[2]Summary!E125</f>
+        <v>0</v>
       </c>
       <c r="E5" s="1">
-        <f>+[1]Summary!F125</f>
+        <f>+[2]Summary!F125</f>
         <v>35.894206480906618</v>
       </c>
       <c r="F5" s="1">
-        <f>+[1]Summary!G125</f>
+        <f>+[2]Summary!G125</f>
         <v>58.217939999999992</v>
       </c>
       <c r="G5" s="1">
@@ -2779,23 +2815,23 @@
         <v>2024</v>
       </c>
       <c r="B6" s="1">
-        <f>+[1]Summary!C126</f>
-        <v>6317.7034984328593</v>
+        <f>+[2]Summary!C126</f>
+        <v>6435.0368317661923</v>
       </c>
       <c r="C6" s="1">
-        <f>+[1]Summary!D126</f>
+        <f>+[2]Summary!D126</f>
         <v>841.1997619199999</v>
       </c>
       <c r="D6" s="1">
-        <f>+[1]Summary!E126</f>
-        <v>117.33333333333333</v>
+        <f>+[2]Summary!E126</f>
+        <v>0</v>
       </c>
       <c r="E6" s="1">
-        <f>+[1]Summary!F126</f>
+        <f>+[2]Summary!F126</f>
         <v>45.707903604683125</v>
       </c>
       <c r="F6" s="1">
-        <f>+[1]Summary!G126</f>
+        <f>+[2]Summary!G126</f>
         <v>57.635760599999998</v>
       </c>
       <c r="G6" s="1">
@@ -2814,23 +2850,23 @@
         <v>2025</v>
       </c>
       <c r="B7" s="1">
-        <f>+[1]Summary!C127</f>
-        <v>6383.1241171309066</v>
+        <f>+[2]Summary!C127</f>
+        <v>6524.7907837975736</v>
       </c>
       <c r="C7" s="1">
-        <f>+[1]Summary!D127</f>
+        <f>+[2]Summary!D127</f>
         <v>824.37576668159988</v>
       </c>
       <c r="D7" s="1">
-        <f>+[1]Summary!E127</f>
-        <v>141.66666666666669</v>
+        <f>+[2]Summary!E127</f>
+        <v>0</v>
       </c>
       <c r="E7" s="1">
-        <f>+[1]Summary!F127</f>
+        <f>+[2]Summary!F127</f>
         <v>55.746159774087921</v>
       </c>
       <c r="F7" s="1">
-        <f>+[1]Summary!G127</f>
+        <f>+[2]Summary!G127</f>
         <v>57.059402993999996</v>
       </c>
       <c r="G7" s="1">
@@ -2849,23 +2885,23 @@
         <v>2026</v>
       </c>
       <c r="B8" s="1">
-        <f>+[1]Summary!C128</f>
-        <v>6446.9901815949561</v>
+        <f>+[2]Summary!C128</f>
+        <v>6612.9901815949561</v>
       </c>
       <c r="C8" s="1">
-        <f>+[1]Summary!D128</f>
+        <f>+[2]Summary!D128</f>
         <v>807.88825134796787</v>
       </c>
       <c r="D8" s="1">
-        <f>+[1]Summary!E128</f>
-        <v>166</v>
+        <f>+[2]Summary!E128</f>
+        <v>0</v>
       </c>
       <c r="E8" s="1">
-        <f>+[1]Summary!F128</f>
+        <f>+[2]Summary!F128</f>
         <v>66.004866089376534</v>
       </c>
       <c r="F8" s="1">
-        <f>+[1]Summary!G128</f>
+        <f>+[2]Summary!G128</f>
         <v>56.488808964059992</v>
       </c>
       <c r="G8" s="1">
@@ -2884,23 +2920,23 @@
         <v>2027</v>
       </c>
       <c r="B9" s="1">
-        <f>+[1]Summary!C129</f>
-        <v>6564.090560325576</v>
+        <f>+[2]Summary!C129</f>
+        <v>6739.6984046017715</v>
       </c>
       <c r="C9" s="1">
-        <f>+[1]Summary!D129</f>
+        <f>+[2]Summary!D129</f>
         <v>791.73048632100847</v>
       </c>
       <c r="D9" s="1">
-        <f>+[1]Summary!E129</f>
-        <v>190.33333333333334</v>
+        <f>+[2]Summary!E129</f>
+        <v>14.725489057137942</v>
       </c>
       <c r="E9" s="1">
-        <f>+[1]Summary!F129</f>
+        <f>+[2]Summary!F129</f>
         <v>76.479957215659979</v>
       </c>
       <c r="F9" s="1">
-        <f>+[1]Summary!G129</f>
+        <f>+[2]Summary!G129</f>
         <v>55.923920874419395</v>
       </c>
       <c r="G9" s="1">
@@ -2919,23 +2955,23 @@
         <v>2028</v>
       </c>
       <c r="B10" s="1">
-        <f>+[1]Summary!C130</f>
-        <v>6679.7139674496757</v>
+        <f>+[2]Summary!C130</f>
+        <v>6830.7888039146947</v>
       </c>
       <c r="C10" s="1">
-        <f>+[1]Summary!D130</f>
+        <f>+[2]Summary!D130</f>
         <v>775.89587659458823</v>
       </c>
       <c r="D10" s="1">
-        <f>+[1]Summary!E130</f>
-        <v>214.66666666666666</v>
+        <f>+[2]Summary!E130</f>
+        <v>63.591830201647646</v>
       </c>
       <c r="E10" s="1">
-        <f>+[1]Summary!F130</f>
+        <f>+[2]Summary!F130</f>
         <v>87.1674110095298</v>
       </c>
       <c r="F10" s="1">
-        <f>+[1]Summary!G130</f>
+        <f>+[2]Summary!G130</f>
         <v>55.364681665675199</v>
       </c>
       <c r="G10" s="1">
@@ -2954,28 +2990,28 @@
         <v>2029</v>
       </c>
       <c r="B11" s="1">
-        <f>+[1]Summary!C131</f>
-        <v>6793.8989724839885</v>
+        <f>+[2]Summary!C131</f>
+        <v>6920.6224940027096</v>
       </c>
       <c r="C11" s="1">
-        <f>+[1]Summary!D131</f>
+        <f>+[2]Summary!D131</f>
         <v>760.3779590626965</v>
       </c>
       <c r="D11" s="1">
-        <f>+[1]Summary!E131</f>
-        <v>239</v>
+        <f>+[2]Summary!E131</f>
+        <v>112.27647848127944</v>
       </c>
       <c r="E11" s="1">
-        <f>+[1]Summary!F131</f>
+        <f>+[2]Summary!F131</f>
         <v>98.063248148529368</v>
       </c>
       <c r="F11" s="1">
-        <f>+[1]Summary!G131</f>
+        <f>+[2]Summary!G131</f>
         <v>54.811034849018441</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" si="0"/>
-        <v>7946.1512145442321</v>
+        <v>7946.151214544233</v>
       </c>
       <c r="H11" t="s">
         <v>6</v>
@@ -2989,23 +3025,23 @@
         <v>2030</v>
       </c>
       <c r="B12" s="1">
-        <f>+[1]Summary!C132</f>
-        <v>6906.684010119664</v>
+        <f>+[2]Summary!C132</f>
+        <v>7009.2378937268386</v>
       </c>
       <c r="C12" s="1">
-        <f>+[1]Summary!D132</f>
+        <f>+[2]Summary!D132</f>
         <v>745.17039988144245</v>
       </c>
       <c r="D12" s="1">
-        <f>+[1]Summary!E132</f>
-        <v>263.33333333333337</v>
+        <f>+[2]Summary!E132</f>
+        <v>160.77944972615859</v>
       </c>
       <c r="E12" s="1">
-        <f>+[1]Summary!F132</f>
+        <f>+[2]Summary!F132</f>
         <v>109.16353176345264</v>
       </c>
       <c r="F12" s="1">
-        <f>+[1]Summary!G132</f>
+        <f>+[2]Summary!G132</f>
         <v>54.262924500528257</v>
       </c>
       <c r="G12" s="1">
@@ -3024,23 +3060,23 @@
         <v>2031</v>
       </c>
       <c r="B13" s="1">
-        <f>+[1]Summary!C133</f>
-        <v>7018.1073900311767</v>
+        <f>+[2]Summary!C133</f>
+        <v>7096.6732670272604</v>
       </c>
       <c r="C13" s="1">
-        <f>+[1]Summary!D133</f>
+        <f>+[2]Summary!D133</f>
         <v>730.2669918838136</v>
       </c>
       <c r="D13" s="1">
-        <f>+[1]Summary!E133</f>
-        <v>287.66666666666669</v>
+        <f>+[2]Summary!E133</f>
+        <v>209.10078967058243</v>
       </c>
       <c r="E13" s="1">
-        <f>+[1]Summary!F133</f>
+        <f>+[2]Summary!F133</f>
         <v>120.4643670734489</v>
       </c>
       <c r="F13" s="1">
-        <f>+[1]Summary!G133</f>
+        <f>+[2]Summary!G133</f>
         <v>53.720295255522977</v>
       </c>
       <c r="G13" s="1">
@@ -3059,23 +3095,23 @@
         <v>2032</v>
       </c>
       <c r="B14" s="1">
-        <f>+[1]Summary!C134</f>
-        <v>7128.2073067128322</v>
+        <f>+[2]Summary!C134</f>
+        <v>7182.9667332657464</v>
       </c>
       <c r="C14" s="1">
-        <f>+[1]Summary!D134</f>
+        <f>+[2]Summary!D134</f>
         <v>715.66165204613731</v>
       </c>
       <c r="D14" s="1">
-        <f>+[1]Summary!E134</f>
-        <v>312</v>
+        <f>+[2]Summary!E134</f>
+        <v>257.24057344708592</v>
       </c>
       <c r="E14" s="1">
-        <f>+[1]Summary!F134</f>
+        <f>+[2]Summary!F134</f>
         <v>131.96190102391498</v>
       </c>
       <c r="F14" s="1">
-        <f>+[1]Summary!G134</f>
+        <f>+[2]Summary!G134</f>
         <v>53.183092302967751</v>
       </c>
       <c r="G14" s="1">
@@ -3094,28 +3130,28 @@
         <v>2033</v>
       </c>
       <c r="B15" s="1">
-        <f>+[1]Summary!C135</f>
-        <v>7237.0218493461707</v>
+        <f>+[2]Summary!C135</f>
+        <v>7268.1562775932571</v>
       </c>
       <c r="C15" s="1">
-        <f>+[1]Summary!D135</f>
+        <f>+[2]Summary!D135</f>
         <v>701.34841900521451</v>
       </c>
       <c r="D15" s="1">
-        <f>+[1]Summary!E135</f>
-        <v>336.33333333333331</v>
+        <f>+[2]Summary!E135</f>
+        <v>305.19890508624633</v>
       </c>
       <c r="E15" s="1">
-        <f>+[1]Summary!F135</f>
+        <f>+[2]Summary!F135</f>
         <v>143.65232192715405</v>
       </c>
       <c r="F15" s="1">
-        <f>+[1]Summary!G135</f>
+        <f>+[2]Summary!G135</f>
         <v>52.651261379938063</v>
       </c>
       <c r="G15" s="1">
         <f t="shared" si="0"/>
-        <v>8471.0071849918131</v>
+        <v>8471.0071849918113</v>
       </c>
       <c r="H15" t="s">
         <v>6</v>
@@ -3129,23 +3165,23 @@
         <v>2034</v>
       </c>
       <c r="B16" s="1">
-        <f>+[1]Summary!C136</f>
-        <v>7344.5890117015188</v>
+        <f>+[2]Summary!C136</f>
+        <v>7352.2797613460125</v>
       </c>
       <c r="C16" s="1">
-        <f>+[1]Summary!D136</f>
+        <f>+[2]Summary!D136</f>
         <v>687.32145062511029</v>
       </c>
       <c r="D16" s="1">
-        <f>+[1]Summary!E136</f>
-        <v>360.66666666666669</v>
+        <f>+[2]Summary!E136</f>
+        <v>352.97591702217233</v>
       </c>
       <c r="E16" s="1">
-        <f>+[1]Summary!F136</f>
+        <f>+[2]Summary!F136</f>
         <v>155.53185910578233</v>
       </c>
       <c r="F16" s="1">
-        <f>+[1]Summary!G136</f>
+        <f>+[2]Summary!G136</f>
         <v>52.124748766138687</v>
       </c>
       <c r="G16" s="1">
@@ -3164,23 +3200,23 @@
         <v>2035</v>
       </c>
       <c r="B17" s="1">
-        <f>+[1]Summary!C137</f>
+        <f>+[2]Summary!C137</f>
         <v>7435.3749324734181</v>
       </c>
       <c r="C17" s="1">
-        <f>+[1]Summary!D137</f>
+        <f>+[2]Summary!D137</f>
         <v>673.575021612608</v>
       </c>
       <c r="D17" s="1">
-        <f>+[1]Summary!E137</f>
+        <f>+[2]Summary!E137</f>
         <v>400.571769603625</v>
       </c>
       <c r="E17" s="1">
-        <f>+[1]Summary!F137</f>
+        <f>+[2]Summary!F137</f>
         <v>167.59678253886366</v>
       </c>
       <c r="F17" s="1">
-        <f>+[1]Summary!G137</f>
+        <f>+[2]Summary!G137</f>
         <v>51.603501278477296</v>
       </c>
       <c r="G17" s="1">
@@ -3199,23 +3235,23 @@
         <v>2036</v>
       </c>
       <c r="B18" s="1">
-        <f>+[1]Summary!C138</f>
+        <f>+[2]Summary!C138</f>
         <v>7517.4794360012529</v>
       </c>
       <c r="C18" s="1">
-        <f>+[1]Summary!D138</f>
+        <f>+[2]Summary!D138</f>
         <v>660.10352118035587</v>
       </c>
       <c r="D18" s="1">
-        <f>+[1]Summary!E138</f>
+        <f>+[2]Summary!E138</f>
         <v>447.98665061071688</v>
       </c>
       <c r="E18" s="1">
-        <f>+[1]Summary!F138</f>
+        <f>+[2]Summary!F138</f>
         <v>179.84340251075258</v>
       </c>
       <c r="F18" s="1">
-        <f>+[1]Summary!G138</f>
+        <f>+[2]Summary!G138</f>
         <v>51.087466265692527</v>
       </c>
       <c r="G18" s="1">
@@ -3234,23 +3270,23 @@
         <v>2037</v>
       </c>
       <c r="B19" s="1">
-        <f>+[1]Summary!C139</f>
+        <f>+[2]Summary!C139</f>
         <v>7598.6308245335194</v>
       </c>
       <c r="C19" s="1">
-        <f>+[1]Summary!D139</f>
+        <f>+[2]Summary!D139</f>
         <v>646.90145075674877</v>
       </c>
       <c r="D19" s="1">
-        <f>+[1]Summary!E139</f>
+        <f>+[2]Summary!E139</f>
         <v>440.47077477713759</v>
       </c>
       <c r="E19" s="1">
-        <f>+[1]Summary!F139</f>
+        <f>+[2]Summary!F139</f>
         <v>192.26806926262711</v>
       </c>
       <c r="F19" s="1">
-        <f>+[1]Summary!G139</f>
+        <f>+[2]Summary!G139</f>
         <v>50.576591603035595</v>
       </c>
       <c r="G19" s="1">
@@ -3269,28 +3305,28 @@
         <v>2038</v>
       </c>
       <c r="B20" s="1">
-        <f>+[1]Summary!C140</f>
-        <v>7653.6409521142259</v>
+        <f>+[2]Summary!C140</f>
+        <v>7678.866568796373</v>
       </c>
       <c r="C20" s="1">
-        <f>+[1]Summary!D140</f>
+        <f>+[2]Summary!D140</f>
         <v>633.96342174161373</v>
       </c>
       <c r="D20" s="1">
-        <f>+[1]Summary!E140</f>
-        <v>458</v>
+        <f>+[2]Summary!E140</f>
+        <v>432.77438331785265</v>
       </c>
       <c r="E20" s="1">
-        <f>+[1]Summary!F140</f>
+        <f>+[2]Summary!F140</f>
         <v>204.86717264669176</v>
       </c>
       <c r="F20" s="1">
-        <f>+[1]Summary!G140</f>
+        <f>+[2]Summary!G140</f>
         <v>50.07082568700524</v>
       </c>
       <c r="G20" s="1">
         <f t="shared" si="0"/>
-        <v>9000.5423721895368</v>
+        <v>9000.5423721895349</v>
       </c>
       <c r="H20" t="s">
         <v>6</v>
@@ -3304,28 +3340,28 @@
         <v>2039</v>
       </c>
       <c r="B21" s="1">
-        <f>+[1]Summary!C141</f>
-        <v>7700.7884783565314</v>
+        <f>+[2]Summary!C141</f>
+        <v>7758.2240682276388</v>
       </c>
       <c r="C21" s="1">
-        <f>+[1]Summary!D141</f>
+        <f>+[2]Summary!D141</f>
         <v>621.28415330678149</v>
       </c>
       <c r="D21" s="1">
-        <f>+[1]Summary!E141</f>
-        <v>482.33333333333331</v>
+        <f>+[2]Summary!E141</f>
+        <v>424.89774346222532</v>
       </c>
       <c r="E21" s="1">
-        <f>+[1]Summary!F141</f>
+        <f>+[2]Summary!F141</f>
         <v>217.63714178303201</v>
       </c>
       <c r="F21" s="1">
-        <f>+[1]Summary!G141</f>
+        <f>+[2]Summary!G141</f>
         <v>49.570117430135184</v>
       </c>
       <c r="G21" s="1">
         <f t="shared" si="0"/>
-        <v>9071.6132242098156</v>
+        <v>9071.6132242098138</v>
       </c>
       <c r="H21" t="s">
         <v>6</v>
@@ -3339,23 +3375,23 @@
         <v>2040</v>
       </c>
       <c r="B22" s="1">
-        <f>+[1]Summary!C142</f>
-        <v>7746.9151429411868</v>
+        <f>+[2]Summary!C142</f>
+        <v>7836.7406616153439</v>
       </c>
       <c r="C22" s="1">
-        <f>+[1]Summary!D142</f>
+        <f>+[2]Summary!D142</f>
         <v>608.85847024064583</v>
       </c>
       <c r="D22" s="1">
-        <f>+[1]Summary!E142</f>
-        <v>506.66666666666669</v>
+        <f>+[2]Summary!E142</f>
+        <v>416.84114799250932</v>
       </c>
       <c r="E22" s="1">
-        <f>+[1]Summary!F142</f>
+        <f>+[2]Summary!F142</f>
         <v>230.57444471910122</v>
       </c>
       <c r="F22" s="1">
-        <f>+[1]Summary!G142</f>
+        <f>+[2]Summary!G142</f>
         <v>49.074416255833839</v>
       </c>
       <c r="G22" s="1">
@@ -3374,23 +3410,23 @@
         <v>2041</v>
       </c>
       <c r="B23" s="1">
-        <f>+[1]Summary!C143</f>
-        <v>7792.0585525764764</v>
+        <f>+[2]Summary!C143</f>
+        <v>7914.4536377888144</v>
       </c>
       <c r="C23" s="1">
-        <f>+[1]Summary!D143</f>
+        <f>+[2]Summary!D143</f>
         <v>596.68130083583287</v>
       </c>
       <c r="D23" s="1">
-        <f>+[1]Summary!E143</f>
-        <v>531</v>
+        <f>+[2]Summary!E143</f>
+        <v>408.60491478766164</v>
       </c>
       <c r="E23" s="1">
-        <f>+[1]Summary!F143</f>
+        <f>+[2]Summary!F143</f>
         <v>243.67558809182165</v>
       </c>
       <c r="F23" s="1">
-        <f>+[1]Summary!G143</f>
+        <f>+[2]Summary!G143</f>
         <v>48.583672093275496</v>
       </c>
       <c r="G23" s="1">
@@ -3409,28 +3445,28 @@
         <v>2042</v>
       </c>
       <c r="B24" s="1">
-        <f>+[1]Summary!C144</f>
-        <v>7836.2562994049604</v>
+        <f>+[2]Summary!C144</f>
+        <v>7991.4002463658671</v>
       </c>
       <c r="C24" s="1">
-        <f>+[1]Summary!D144</f>
+        <f>+[2]Summary!D144</f>
         <v>584.74767481911624</v>
       </c>
       <c r="D24" s="1">
-        <f>+[1]Summary!E144</f>
-        <v>555.33333333333337</v>
+        <f>+[2]Summary!E144</f>
+        <v>400.18938637242582</v>
       </c>
       <c r="E24" s="1">
-        <f>+[1]Summary!F144</f>
+        <f>+[2]Summary!F144</f>
         <v>256.93711679228062</v>
       </c>
       <c r="F24" s="1">
-        <f>+[1]Summary!G144</f>
+        <f>+[2]Summary!G144</f>
         <v>48.097835372342736</v>
       </c>
       <c r="G24" s="1">
         <f t="shared" si="0"/>
-        <v>9281.372259722033</v>
+        <v>9281.3722597220312</v>
       </c>
       <c r="H24" t="s">
         <v>6</v>
@@ -3444,23 +3480,23 @@
         <v>2043</v>
       </c>
       <c r="B25" s="1">
-        <f>+[1]Summary!C145</f>
-        <v>7879.5459713646242</v>
+        <f>+[2]Summary!C145</f>
+        <v>8067.6177085596555</v>
       </c>
       <c r="C25" s="1">
-        <f>+[1]Summary!D145</f>
+        <f>+[2]Summary!D145</f>
         <v>573.05272132273387</v>
       </c>
       <c r="D25" s="1">
-        <f>+[1]Summary!E145</f>
-        <v>579.66666666666663</v>
+        <f>+[2]Summary!E145</f>
+        <v>391.59492947163466</v>
       </c>
       <c r="E25" s="1">
-        <f>+[1]Summary!F145</f>
+        <f>+[2]Summary!F145</f>
         <v>270.35561363300349</v>
       </c>
       <c r="F25" s="1">
-        <f>+[1]Summary!G145</f>
+        <f>+[2]Summary!G145</f>
         <v>47.616857018619314</v>
       </c>
       <c r="G25" s="1">
@@ -3479,28 +3515,28 @@
         <v>2044</v>
       </c>
       <c r="B26" s="1">
-        <f>+[1]Summary!C146</f>
-        <v>7921.9651626184632</v>
+        <f>+[2]Summary!C146</f>
+        <v>8143.1432280487788</v>
       </c>
       <c r="C26" s="1">
-        <f>+[1]Summary!D146</f>
+        <f>+[2]Summary!D146</f>
         <v>561.59166689627921</v>
       </c>
       <c r="D26" s="1">
-        <f>+[1]Summary!E146</f>
-        <v>604</v>
+        <f>+[2]Summary!E146</f>
+        <v>382.82193456968452</v>
       </c>
       <c r="E26" s="1">
-        <f>+[1]Summary!F146</f>
+        <f>+[2]Summary!F146</f>
         <v>283.92769901778536</v>
       </c>
       <c r="F26" s="1">
-        <f>+[1]Summary!G146</f>
+        <f>+[2]Summary!G146</f>
         <v>47.140688448433117</v>
       </c>
       <c r="G26" s="1">
         <f t="shared" si="0"/>
-        <v>9418.6252169809613</v>
+        <v>9418.6252169809632</v>
       </c>
       <c r="H26" t="s">
         <v>6</v>
@@ -3514,28 +3550,28 @@
         <v>2045</v>
       </c>
       <c r="B27" s="1">
-        <f>+[1]Summary!C147</f>
-        <v>7963.5514840560863</v>
+        <f>+[2]Summary!C147</f>
+        <v>8218.0140019142891</v>
       </c>
       <c r="C27" s="1">
-        <f>+[1]Summary!D147</f>
+        <f>+[2]Summary!D147</f>
         <v>550.35983355835356</v>
       </c>
       <c r="D27" s="1">
-        <f>+[1]Summary!E147</f>
-        <v>628.33333333333337</v>
+        <f>+[2]Summary!E147</f>
+        <v>373.8708154751302</v>
       </c>
       <c r="E27" s="1">
-        <f>+[1]Summary!F147</f>
+        <f>+[2]Summary!F147</f>
         <v>297.65003061406253</v>
       </c>
       <c r="F27" s="1">
-        <f>+[1]Summary!G147</f>
+        <f>+[2]Summary!G147</f>
         <v>46.669281563948786</v>
       </c>
       <c r="G27" s="1">
         <f t="shared" si="0"/>
-        <v>9486.5639631257854</v>
+        <v>9486.5639631257836</v>
       </c>
       <c r="H27" t="s">
         <v>6</v>
@@ -3549,23 +3585,23 @@
         <v>2046</v>
       </c>
       <c r="B28" s="1">
-        <f>+[1]Summary!C148</f>
-        <v>8004.3425738709338</v>
+        <f>+[2]Summary!C148</f>
+        <v>8292.2672316472472</v>
       </c>
       <c r="C28" s="1">
-        <f>+[1]Summary!D148</f>
+        <f>+[2]Summary!D148</f>
         <v>539.35263688718646</v>
       </c>
       <c r="D28" s="1">
-        <f>+[1]Summary!E148</f>
-        <v>652.66666666666663</v>
+        <f>+[2]Summary!E148</f>
+        <v>364.74200889035319</v>
       </c>
       <c r="E28" s="1">
-        <f>+[1]Summary!F148</f>
+        <f>+[2]Summary!F148</f>
         <v>311.51930302780704</v>
       </c>
       <c r="F28" s="1">
-        <f>+[1]Summary!G148</f>
+        <f>+[2]Summary!G148</f>
         <v>46.202588748309296</v>
       </c>
       <c r="G28" s="1">
@@ -3584,23 +3620,23 @@
         <v>2047</v>
       </c>
       <c r="B29" s="1">
-        <f>+[1]Summary!C149</f>
-        <v>8044.3761082167875</v>
+        <f>+[2]Summary!C149</f>
+        <v>8365.9401342305337</v>
       </c>
       <c r="C29" s="1">
-        <f>+[1]Summary!D149</f>
+        <f>+[2]Summary!D149</f>
         <v>528.56558414944266</v>
       </c>
       <c r="D29" s="1">
-        <f>+[1]Summary!E149</f>
-        <v>677</v>
+        <f>+[2]Summary!E149</f>
+        <v>355.43597398625434</v>
       </c>
       <c r="E29" s="1">
-        <f>+[1]Summary!F149</f>
+        <f>+[2]Summary!F149</f>
         <v>325.53224748092481</v>
       </c>
       <c r="F29" s="1">
-        <f>+[1]Summary!G149</f>
+        <f>+[2]Summary!G149</f>
         <v>45.740562860826209</v>
       </c>
       <c r="G29" s="1">
@@ -3619,23 +3655,23 @@
         <v>2048</v>
       </c>
       <c r="B30" s="1">
-        <f>+[1]Summary!C150</f>
-        <v>8083.6898119472444</v>
+        <f>+[2]Summary!C150</f>
+        <v>8439.0699532986546</v>
       </c>
       <c r="C30" s="1">
-        <f>+[1]Summary!D150</f>
+        <f>+[2]Summary!D150</f>
         <v>517.99427246645382</v>
       </c>
       <c r="D30" s="1">
-        <f>+[1]Summary!E150</f>
-        <v>701.33333333333337</v>
+        <f>+[2]Summary!E150</f>
+        <v>345.9531919819234</v>
       </c>
       <c r="E30" s="1">
-        <f>+[1]Summary!F150</f>
+        <f>+[2]Summary!F150</f>
         <v>339.68563149114044</v>
       </c>
       <c r="F30" s="1">
-        <f>+[1]Summary!G150</f>
+        <f>+[2]Summary!G150</f>
         <v>45.283157232217938</v>
       </c>
       <c r="G30" s="1">
@@ -3654,28 +3690,28 @@
         <v>2049</v>
       </c>
       <c r="B31" s="1">
-        <f>+[1]Summary!C151</f>
-        <v>8122.3214694418766</v>
+        <f>+[2]Summary!C151</f>
+        <v>8511.6939703793068</v>
       </c>
       <c r="C31" s="1">
-        <f>+[1]Summary!D151</f>
+        <f>+[2]Summary!D151</f>
         <v>507.63438701712477</v>
       </c>
       <c r="D31" s="1">
-        <f>+[1]Summary!E151</f>
-        <v>725.66666666666663</v>
+        <f>+[2]Summary!E151</f>
+        <v>336.29416572923748</v>
       </c>
       <c r="E31" s="1">
-        <f>+[1]Summary!F151</f>
+        <f>+[2]Summary!F151</f>
         <v>353.97625855435058</v>
       </c>
       <c r="F31" s="1">
-        <f>+[1]Summary!G151</f>
+        <f>+[2]Summary!G151</f>
         <v>44.830325659895756</v>
       </c>
       <c r="G31" s="1">
         <f t="shared" si="0"/>
-        <v>9754.4291073399127</v>
+        <v>9754.4291073399145</v>
       </c>
       <c r="H31" t="s">
         <v>6</v>
@@ -3689,23 +3725,23 @@
         <v>2050</v>
       </c>
       <c r="B32" s="1">
-        <f>+[1]Summary!C152</f>
-        <v>8160.3089355228558</v>
+        <f>+[2]Summary!C152</f>
+        <v>8583.8495162205127</v>
       </c>
       <c r="C32" s="1">
-        <f>+[1]Summary!D152</f>
+        <f>+[2]Summary!D152</f>
         <v>497.48169927678225</v>
       </c>
       <c r="D32" s="1">
-        <f>+[1]Summary!E152</f>
-        <v>750</v>
+        <f>+[2]Summary!E152</f>
+        <v>326.45941930234289</v>
       </c>
       <c r="E32" s="1">
-        <f>+[1]Summary!F152</f>
+        <f>+[2]Summary!F152</f>
         <v>368.40096782942845</v>
       </c>
       <c r="F32" s="1">
-        <f>+[1]Summary!G152</f>
+        <f>+[2]Summary!G152</f>
         <v>44.382022403296808</v>
       </c>
       <c r="G32" s="1">
@@ -3724,23 +3760,23 @@
         <v>2020</v>
       </c>
       <c r="B33" s="1">
-        <f>+[1]Summary!C153</f>
-        <v>6039.6921628399505</v>
+        <f>+[2]Summary!C153</f>
+        <v>6059.6921628399505</v>
       </c>
       <c r="C33" s="1">
-        <f>+[1]Summary!D153</f>
+        <f>+[2]Summary!D153</f>
         <v>912</v>
       </c>
       <c r="D33" s="1">
-        <f>+[1]Summary!E153</f>
-        <v>20</v>
+        <f>+[2]Summary!E153</f>
+        <v>0</v>
       </c>
       <c r="E33" s="1">
-        <f>+[1]Summary!F153</f>
+        <f>+[2]Summary!F153</f>
         <v>7.8422197749500002</v>
       </c>
       <c r="F33" s="1">
-        <f>+[1]Summary!G153</f>
+        <f>+[2]Summary!G153</f>
         <v>60</v>
       </c>
       <c r="G33" s="1">
@@ -3759,23 +3795,23 @@
         <v>2021</v>
       </c>
       <c r="B34" s="1">
-        <f>+[1]Summary!C154</f>
-        <v>6120.0692065962767</v>
+        <f>+[2]Summary!C154</f>
+        <v>6164.4025399296097</v>
       </c>
       <c r="C34" s="1">
-        <f>+[1]Summary!D154</f>
+        <f>+[2]Summary!D154</f>
         <v>893.76</v>
       </c>
       <c r="D34" s="1">
-        <f>+[1]Summary!E154</f>
-        <v>44.333333333333329</v>
+        <f>+[2]Summary!E154</f>
+        <v>0</v>
       </c>
       <c r="E34" s="1">
-        <f>+[1]Summary!F154</f>
+        <f>+[2]Summary!F154</f>
         <v>8.6110502226513645</v>
       </c>
       <c r="F34" s="1">
-        <f>+[1]Summary!G154</f>
+        <f>+[2]Summary!G154</f>
         <v>59.4</v>
       </c>
       <c r="G34" s="1">
@@ -3794,23 +3830,23 @@
         <v>2022</v>
       </c>
       <c r="B35" s="1">
-        <f>+[1]Summary!C155</f>
-        <v>6198.9553648044894</v>
+        <f>+[2]Summary!C155</f>
+        <v>6267.6220314711563</v>
       </c>
       <c r="C35" s="1">
-        <f>+[1]Summary!D155</f>
+        <f>+[2]Summary!D155</f>
         <v>875.88479999999993</v>
       </c>
       <c r="D35" s="1">
-        <f>+[1]Summary!E155</f>
-        <v>68.666666666666657</v>
+        <f>+[2]Summary!E155</f>
+        <v>0</v>
       </c>
       <c r="E35" s="1">
-        <f>+[1]Summary!F155</f>
+        <f>+[2]Summary!F155</f>
         <v>9.3961504441431867</v>
       </c>
       <c r="F35" s="1">
-        <f>+[1]Summary!G155</f>
+        <f>+[2]Summary!G155</f>
         <v>58.805999999999997</v>
       </c>
       <c r="G35" s="1">
@@ -3829,23 +3865,23 @@
         <v>2023</v>
       </c>
       <c r="B36" s="1">
-        <f>+[1]Summary!C156</f>
-        <v>6276.3862816116016</v>
+        <f>+[2]Summary!C156</f>
+        <v>6369.3862816116016</v>
       </c>
       <c r="C36" s="1">
-        <f>+[1]Summary!D156</f>
+        <f>+[2]Summary!D156</f>
         <v>858.36710399999993</v>
       </c>
       <c r="D36" s="1">
-        <f>+[1]Summary!E156</f>
-        <v>93</v>
+        <f>+[2]Summary!E156</f>
+        <v>0</v>
       </c>
       <c r="E36" s="1">
-        <f>+[1]Summary!F156</f>
+        <f>+[2]Summary!F156</f>
         <v>10.197217750257561</v>
       </c>
       <c r="F36" s="1">
-        <f>+[1]Summary!G156</f>
+        <f>+[2]Summary!G156</f>
         <v>58.217939999999992</v>
       </c>
       <c r="G36" s="1">
@@ -3864,23 +3900,23 @@
         <v>2024</v>
       </c>
       <c r="B37" s="1">
-        <f>+[1]Summary!C157</f>
-        <v>6352.3974493617143</v>
+        <f>+[2]Summary!C157</f>
+        <v>6469.7307826950473</v>
       </c>
       <c r="C37" s="1">
-        <f>+[1]Summary!D157</f>
+        <f>+[2]Summary!D157</f>
         <v>841.1997619199999</v>
       </c>
       <c r="D37" s="1">
-        <f>+[1]Summary!E157</f>
-        <v>117.33333333333333</v>
+        <f>+[2]Summary!E157</f>
+        <v>0</v>
       </c>
       <c r="E37" s="1">
-        <f>+[1]Summary!F157</f>
+        <f>+[2]Summary!F157</f>
         <v>11.013952675827259</v>
       </c>
       <c r="F37" s="1">
-        <f>+[1]Summary!G157</f>
+        <f>+[2]Summary!G157</f>
         <v>57.635760599999998</v>
       </c>
       <c r="G37" s="1">
@@ -3899,23 +3935,23 @@
         <v>2025</v>
       </c>
       <c r="B38" s="1">
-        <f>+[1]Summary!C158</f>
-        <v>6427.0242179530005</v>
+        <f>+[2]Summary!C158</f>
+        <v>6568.6908846196675</v>
       </c>
       <c r="C38" s="1">
-        <f>+[1]Summary!D158</f>
+        <f>+[2]Summary!D158</f>
         <v>824.37576668159988</v>
       </c>
       <c r="D38" s="1">
-        <f>+[1]Summary!E158</f>
-        <v>141.66666666666669</v>
+        <f>+[2]Summary!E158</f>
+        <v>0</v>
       </c>
       <c r="E38" s="1">
-        <f>+[1]Summary!F158</f>
+        <f>+[2]Summary!F158</f>
         <v>11.846058951993687</v>
       </c>
       <c r="F38" s="1">
-        <f>+[1]Summary!G158</f>
+        <f>+[2]Summary!G158</f>
         <v>57.059402993999996</v>
       </c>
       <c r="G38" s="1">
@@ -3934,23 +3970,23 @@
         <v>2026</v>
       </c>
       <c r="B39" s="1">
-        <f>+[1]Summary!C159</f>
-        <v>6500.3018042056065</v>
+        <f>+[2]Summary!C159</f>
+        <v>6666.3018042056065</v>
       </c>
       <c r="C39" s="1">
-        <f>+[1]Summary!D159</f>
+        <f>+[2]Summary!D159</f>
         <v>807.88825134796787</v>
       </c>
       <c r="D39" s="1">
-        <f>+[1]Summary!E159</f>
-        <v>166</v>
+        <f>+[2]Summary!E159</f>
+        <v>0</v>
       </c>
       <c r="E39" s="1">
-        <f>+[1]Summary!F159</f>
+        <f>+[2]Summary!F159</f>
         <v>12.693243478726256</v>
       </c>
       <c r="F39" s="1">
-        <f>+[1]Summary!G159</f>
+        <f>+[2]Summary!G159</f>
         <v>56.488808964059992</v>
       </c>
       <c r="G39" s="1">
@@ -3969,23 +4005,23 @@
         <v>2027</v>
       </c>
       <c r="B40" s="1">
-        <f>+[1]Summary!C160</f>
-        <v>6578.4103326319082</v>
+        <f>+[2]Summary!C160</f>
+        <v>6768.7436659652412</v>
       </c>
       <c r="C40" s="1">
-        <f>+[1]Summary!D160</f>
+        <f>+[2]Summary!D160</f>
         <v>791.73048632100847</v>
       </c>
       <c r="D40" s="1">
-        <f>+[1]Summary!E160</f>
-        <v>190.33333333333334</v>
+        <f>+[2]Summary!E160</f>
+        <v>0</v>
       </c>
       <c r="E40" s="1">
-        <f>+[1]Summary!F160</f>
+        <f>+[2]Summary!F160</f>
         <v>7.4101849093282492</v>
       </c>
       <c r="F40" s="1">
-        <f>+[1]Summary!G160</f>
+        <f>+[2]Summary!G160</f>
         <v>55.923920874419395</v>
       </c>
       <c r="G40" s="1">
@@ -4004,23 +4040,23 @@
         <v>2028</v>
       </c>
       <c r="B41" s="1">
-        <f>+[1]Summary!C161</f>
-        <v>6649.3958430135181</v>
+        <f>+[2]Summary!C161</f>
+        <v>6864.062509680185</v>
       </c>
       <c r="C41" s="1">
-        <f>+[1]Summary!D161</f>
+        <f>+[2]Summary!D161</f>
         <v>775.89587659458823</v>
       </c>
       <c r="D41" s="1">
-        <f>+[1]Summary!E161</f>
-        <v>214.66666666666666</v>
+        <f>+[2]Summary!E161</f>
+        <v>0</v>
       </c>
       <c r="E41" s="1">
-        <f>+[1]Summary!F161</f>
+        <f>+[2]Summary!F161</f>
         <v>7.9855354456854011</v>
       </c>
       <c r="F41" s="1">
-        <f>+[1]Summary!G161</f>
+        <f>+[2]Summary!G161</f>
         <v>55.364681665675199</v>
       </c>
       <c r="G41" s="1">
@@ -4039,23 +4075,23 @@
         <v>2029</v>
       </c>
       <c r="B42" s="1">
-        <f>+[1]Summary!C162</f>
-        <v>6719.1316864195223</v>
+        <f>+[2]Summary!C162</f>
+        <v>6958.1316864195223</v>
       </c>
       <c r="C42" s="1">
-        <f>+[1]Summary!D162</f>
+        <f>+[2]Summary!D162</f>
         <v>760.3779590626965</v>
       </c>
       <c r="D42" s="1">
-        <f>+[1]Summary!E162</f>
-        <v>239</v>
+        <f>+[2]Summary!E162</f>
+        <v>0</v>
       </c>
       <c r="E42" s="1">
-        <f>+[1]Summary!F162</f>
+        <f>+[2]Summary!F162</f>
         <v>8.5805342129963194</v>
       </c>
       <c r="F42" s="1">
-        <f>+[1]Summary!G162</f>
+        <f>+[2]Summary!G162</f>
         <v>54.811034849018441</v>
       </c>
       <c r="G42" s="1">
@@ -4074,23 +4110,23 @@
         <v>2030</v>
       </c>
       <c r="B43" s="1">
-        <f>+[1]Summary!C163</f>
-        <v>6787.6522353787177</v>
+        <f>+[2]Summary!C163</f>
+        <v>7050.9855687120507</v>
       </c>
       <c r="C43" s="1">
-        <f>+[1]Summary!D163</f>
+        <f>+[2]Summary!D163</f>
         <v>745.17039988144245</v>
       </c>
       <c r="D43" s="1">
-        <f>+[1]Summary!E163</f>
-        <v>263.33333333333337</v>
+        <f>+[2]Summary!E163</f>
+        <v>0</v>
       </c>
       <c r="E43" s="1">
-        <f>+[1]Summary!F163</f>
+        <f>+[2]Summary!F163</f>
         <v>9.195306504398939</v>
       </c>
       <c r="F43" s="1">
-        <f>+[1]Summary!G163</f>
+        <f>+[2]Summary!G163</f>
         <v>54.262924500528257</v>
       </c>
       <c r="G43" s="1">
@@ -4109,23 +4145,23 @@
         <v>2031</v>
       </c>
       <c r="B44" s="1">
-        <f>+[1]Summary!C164</f>
-        <v>6854.9917852369981</v>
+        <f>+[2]Summary!C164</f>
+        <v>7142.6584519036651</v>
       </c>
       <c r="C44" s="1">
-        <f>+[1]Summary!D164</f>
+        <f>+[2]Summary!D164</f>
         <v>730.2669918838136</v>
       </c>
       <c r="D44" s="1">
-        <f>+[1]Summary!E164</f>
-        <v>287.66666666666669</v>
+        <f>+[2]Summary!E164</f>
+        <v>0</v>
       </c>
       <c r="E44" s="1">
-        <f>+[1]Summary!F164</f>
+        <f>+[2]Summary!F164</f>
         <v>9.8299718676271439</v>
       </c>
       <c r="F44" s="1">
-        <f>+[1]Summary!G164</f>
+        <f>+[2]Summary!G164</f>
         <v>53.720295255522977</v>
       </c>
       <c r="G44" s="1">
@@ -4144,23 +4180,23 @@
         <v>2032</v>
       </c>
       <c r="B45" s="1">
-        <f>+[1]Summary!C165</f>
-        <v>6921.1845635458058</v>
+        <f>+[2]Summary!C165</f>
+        <v>7233.1845635458058</v>
       </c>
       <c r="C45" s="1">
-        <f>+[1]Summary!D165</f>
+        <f>+[2]Summary!D165</f>
         <v>715.66165204613731</v>
       </c>
       <c r="D45" s="1">
-        <f>+[1]Summary!E165</f>
-        <v>312</v>
+        <f>+[2]Summary!E165</f>
+        <v>0</v>
       </c>
       <c r="E45" s="1">
-        <f>+[1]Summary!F165</f>
+        <f>+[2]Summary!F165</f>
         <v>10.484644190941186</v>
       </c>
       <c r="F45" s="1">
-        <f>+[1]Summary!G165</f>
+        <f>+[2]Summary!G165</f>
         <v>53.183092302967751</v>
       </c>
       <c r="G45" s="1">
@@ -4179,28 +4215,28 @@
         <v>2033</v>
       </c>
       <c r="B46" s="1">
-        <f>+[1]Summary!C166</f>
-        <v>6986.2647394851974</v>
+        <f>+[2]Summary!C166</f>
+        <v>7322.5980728185305</v>
       </c>
       <c r="C46" s="1">
-        <f>+[1]Summary!D166</f>
+        <f>+[2]Summary!D166</f>
         <v>701.34841900521451</v>
       </c>
       <c r="D46" s="1">
-        <f>+[1]Summary!E166</f>
-        <v>336.33333333333331</v>
+        <f>+[2]Summary!E166</f>
+        <v>0</v>
       </c>
       <c r="E46" s="1">
-        <f>+[1]Summary!F166</f>
+        <f>+[2]Summary!F166</f>
         <v>11.159431788126373</v>
       </c>
       <c r="F46" s="1">
-        <f>+[1]Summary!G166</f>
+        <f>+[2]Summary!G166</f>
         <v>52.651261379938063</v>
       </c>
       <c r="G46" s="1">
         <f t="shared" si="0"/>
-        <v>8087.7571849918095</v>
+        <v>8087.7571849918086</v>
       </c>
       <c r="H46" t="s">
         <v>7</v>
@@ -4214,23 +4250,23 @@
         <v>2034</v>
       </c>
       <c r="B47" s="1">
-        <f>+[1]Summary!C167</f>
-        <v>7050.2664333247303</v>
+        <f>+[2]Summary!C167</f>
+        <v>7410.9330999913973</v>
       </c>
       <c r="C47" s="1">
-        <f>+[1]Summary!D167</f>
+        <f>+[2]Summary!D167</f>
         <v>687.32145062511029</v>
       </c>
       <c r="D47" s="1">
-        <f>+[1]Summary!E167</f>
-        <v>360.66666666666669</v>
+        <f>+[2]Summary!E167</f>
+        <v>0</v>
       </c>
       <c r="E47" s="1">
-        <f>+[1]Summary!F167</f>
+        <f>+[2]Summary!F167</f>
         <v>11.854437482568521</v>
       </c>
       <c r="F47" s="1">
-        <f>+[1]Summary!G167</f>
+        <f>+[2]Summary!G167</f>
         <v>52.124748766138687</v>
       </c>
       <c r="G47" s="1">
@@ -4249,23 +4285,23 @@
         <v>2035</v>
       </c>
       <c r="B48" s="1">
-        <f>+[1]Summary!C168</f>
-        <v>7113.2237259254916</v>
+        <f>+[2]Summary!C168</f>
+        <v>7498.2237259254916</v>
       </c>
       <c r="C48" s="1">
-        <f>+[1]Summary!D168</f>
+        <f>+[2]Summary!D168</f>
         <v>673.575021612608</v>
       </c>
       <c r="D48" s="1">
-        <f>+[1]Summary!E168</f>
-        <v>385</v>
+        <f>+[2]Summary!E168</f>
+        <v>0</v>
       </c>
       <c r="E48" s="1">
-        <f>+[1]Summary!F168</f>
+        <f>+[2]Summary!F168</f>
         <v>12.569758690414773</v>
       </c>
       <c r="F48" s="1">
-        <f>+[1]Summary!G168</f>
+        <f>+[2]Summary!G168</f>
         <v>51.603501278477296</v>
       </c>
       <c r="G48" s="1">
@@ -4284,23 +4320,23 @@
         <v>2036</v>
       </c>
       <c r="B49" s="1">
-        <f>+[1]Summary!C169</f>
-        <v>7175.1706682865606</v>
+        <f>+[2]Summary!C169</f>
+        <v>7584.5040016198936</v>
       </c>
       <c r="C49" s="1">
-        <f>+[1]Summary!D169</f>
+        <f>+[2]Summary!D169</f>
         <v>660.10352118035587</v>
       </c>
       <c r="D49" s="1">
-        <f>+[1]Summary!E169</f>
-        <v>409.33333333333331</v>
+        <f>+[2]Summary!E169</f>
+        <v>0</v>
       </c>
       <c r="E49" s="1">
-        <f>+[1]Summary!F169</f>
+        <f>+[2]Summary!F169</f>
         <v>13.305487502828036</v>
       </c>
       <c r="F49" s="1">
-        <f>+[1]Summary!G169</f>
+        <f>+[2]Summary!G169</f>
         <v>51.087466265692527</v>
       </c>
       <c r="G49" s="1">
@@ -4319,23 +4355,23 @@
         <v>2037</v>
       </c>
       <c r="B50" s="1">
-        <f>+[1]Summary!C170</f>
-        <v>7236.1412911392736</v>
+        <f>+[2]Summary!C170</f>
+        <v>7669.8079578059405</v>
       </c>
       <c r="C50" s="1">
-        <f>+[1]Summary!D170</f>
+        <f>+[2]Summary!D170</f>
         <v>646.90145075674877</v>
       </c>
       <c r="D50" s="1">
-        <f>+[1]Summary!E170</f>
-        <v>433.66666666666669</v>
+        <f>+[2]Summary!E170</f>
+        <v>0</v>
       </c>
       <c r="E50" s="1">
-        <f>+[1]Summary!F170</f>
+        <f>+[2]Summary!F170</f>
         <v>14.061710767343449</v>
       </c>
       <c r="F50" s="1">
-        <f>+[1]Summary!G170</f>
+        <f>+[2]Summary!G170</f>
         <v>50.576591603035595</v>
       </c>
       <c r="G50" s="1">
@@ -4354,23 +4390,23 @@
         <v>2038</v>
       </c>
       <c r="B51" s="1">
-        <f>+[1]Summary!C171</f>
-        <v>7296.1696145925835</v>
+        <f>+[2]Summary!C171</f>
+        <v>7754.1696145925835</v>
       </c>
       <c r="C51" s="1">
-        <f>+[1]Summary!D171</f>
+        <f>+[2]Summary!D171</f>
         <v>633.96342174161373</v>
       </c>
       <c r="D51" s="1">
-        <f>+[1]Summary!E171</f>
-        <v>458</v>
+        <f>+[2]Summary!E171</f>
+        <v>0</v>
       </c>
       <c r="E51" s="1">
-        <f>+[1]Summary!F171</f>
+        <f>+[2]Summary!F171</f>
         <v>14.838510168335148</v>
       </c>
       <c r="F51" s="1">
-        <f>+[1]Summary!G171</f>
+        <f>+[2]Summary!G171</f>
         <v>50.07082568700524</v>
       </c>
       <c r="G51" s="1">
@@ -4389,23 +4425,23 @@
         <v>2039</v>
       </c>
       <c r="B52" s="1">
-        <f>+[1]Summary!C172</f>
-        <v>7355.289657832961</v>
+        <f>+[2]Summary!C172</f>
+        <v>7837.622991166294</v>
       </c>
       <c r="C52" s="1">
-        <f>+[1]Summary!D172</f>
+        <f>+[2]Summary!D172</f>
         <v>621.28415330678149</v>
       </c>
       <c r="D52" s="1">
-        <f>+[1]Summary!E172</f>
-        <v>482.33333333333331</v>
+        <f>+[2]Summary!E172</f>
+        <v>0</v>
       </c>
       <c r="E52" s="1">
-        <f>+[1]Summary!F172</f>
+        <f>+[2]Summary!F172</f>
         <v>15.635962306601458</v>
       </c>
       <c r="F52" s="1">
-        <f>+[1]Summary!G172</f>
+        <f>+[2]Summary!G172</f>
         <v>49.570117430135184</v>
       </c>
       <c r="G52" s="1">
@@ -4424,23 +4460,23 @@
         <v>2040</v>
       </c>
       <c r="B53" s="1">
-        <f>+[1]Summary!C173</f>
-        <v>7413.5354488822113</v>
+        <f>+[2]Summary!C173</f>
+        <v>7920.2021155488783</v>
       </c>
       <c r="C53" s="1">
-        <f>+[1]Summary!D173</f>
+        <f>+[2]Summary!D173</f>
         <v>608.85847024064583</v>
       </c>
       <c r="D53" s="1">
-        <f>+[1]Summary!E173</f>
-        <v>506.66666666666669</v>
+        <f>+[2]Summary!E173</f>
+        <v>0</v>
       </c>
       <c r="E53" s="1">
-        <f>+[1]Summary!F173</f>
+        <f>+[2]Summary!F173</f>
         <v>16.454138778076707</v>
       </c>
       <c r="F53" s="1">
-        <f>+[1]Summary!G173</f>
+        <f>+[2]Summary!G173</f>
         <v>49.074416255833839</v>
       </c>
       <c r="G53" s="1">
@@ -4459,23 +4495,23 @@
         <v>2041</v>
       </c>
       <c r="B54" s="1">
-        <f>+[1]Summary!C174</f>
-        <v>7470.9410344166208</v>
+        <f>+[2]Summary!C174</f>
+        <v>8001.9410344166208</v>
       </c>
       <c r="C54" s="1">
-        <f>+[1]Summary!D174</f>
+        <f>+[2]Summary!D174</f>
         <v>596.68130083583287</v>
       </c>
       <c r="D54" s="1">
-        <f>+[1]Summary!E174</f>
-        <v>531</v>
+        <f>+[2]Summary!E174</f>
+        <v>0</v>
       </c>
       <c r="E54" s="1">
-        <f>+[1]Summary!F174</f>
+        <f>+[2]Summary!F174</f>
         <v>17.293106251677663</v>
       </c>
       <c r="F54" s="1">
-        <f>+[1]Summary!G174</f>
+        <f>+[2]Summary!G174</f>
         <v>48.583672093275496</v>
       </c>
       <c r="G54" s="1">
@@ -4494,28 +4530,28 @@
         <v>2042</v>
       </c>
       <c r="B55" s="1">
-        <f>+[1]Summary!C175</f>
-        <v>7527.5404896509481</v>
+        <f>+[2]Summary!C175</f>
+        <v>8082.8738229842811</v>
       </c>
       <c r="C55" s="1">
-        <f>+[1]Summary!D175</f>
+        <f>+[2]Summary!D175</f>
         <v>584.74767481911624</v>
       </c>
       <c r="D55" s="1">
-        <f>+[1]Summary!E175</f>
-        <v>555.33333333333337</v>
+        <f>+[2]Summary!E175</f>
+        <v>0</v>
       </c>
       <c r="E55" s="1">
-        <f>+[1]Summary!F175</f>
+        <f>+[2]Summary!F175</f>
         <v>18.152926546292662</v>
       </c>
       <c r="F55" s="1">
-        <f>+[1]Summary!G175</f>
+        <f>+[2]Summary!G175</f>
         <v>48.097835372342736</v>
       </c>
       <c r="G55" s="1">
         <f t="shared" si="0"/>
-        <v>8733.872259722033</v>
+        <v>8733.8722597220312</v>
       </c>
       <c r="H55" t="s">
         <v>7</v>
@@ -4529,23 +4565,23 @@
         <v>2043</v>
       </c>
       <c r="B56" s="1">
-        <f>+[1]Summary!C176</f>
-        <v>7583.3679282907042</v>
+        <f>+[2]Summary!C176</f>
+        <v>8163.0345949573712</v>
       </c>
       <c r="C56" s="1">
-        <f>+[1]Summary!D176</f>
+        <f>+[2]Summary!D176</f>
         <v>573.05272132273387</v>
       </c>
       <c r="D56" s="1">
-        <f>+[1]Summary!E176</f>
-        <v>579.66666666666663</v>
+        <f>+[2]Summary!E176</f>
+        <v>0</v>
       </c>
       <c r="E56" s="1">
-        <f>+[1]Summary!F176</f>
+        <f>+[2]Summary!F176</f>
         <v>19.033656706921217</v>
       </c>
       <c r="F56" s="1">
-        <f>+[1]Summary!G176</f>
+        <f>+[2]Summary!G176</f>
         <v>47.616857018619314</v>
       </c>
       <c r="G56" s="1">
@@ -4564,28 +4600,28 @@
         <v>2044</v>
       </c>
       <c r="B57" s="1">
-        <f>+[1]Summary!C177</f>
-        <v>7638.457512556276</v>
+        <f>+[2]Summary!C177</f>
+        <v>8242.4575125562769</v>
       </c>
       <c r="C57" s="1">
-        <f>+[1]Summary!D177</f>
+        <f>+[2]Summary!D177</f>
         <v>561.59166689627921</v>
       </c>
       <c r="D57" s="1">
-        <f>+[1]Summary!E177</f>
-        <v>604</v>
+        <f>+[2]Summary!E177</f>
+        <v>0</v>
       </c>
       <c r="E57" s="1">
-        <f>+[1]Summary!F177</f>
+        <f>+[2]Summary!F177</f>
         <v>19.935349079972163</v>
       </c>
       <c r="F57" s="1">
-        <f>+[1]Summary!G177</f>
+        <f>+[2]Summary!G177</f>
         <v>47.140688448433117</v>
       </c>
       <c r="G57" s="1">
         <f t="shared" si="0"/>
-        <v>8871.1252169809595</v>
+        <v>8871.1252169809613</v>
       </c>
       <c r="H57" t="s">
         <v>7</v>
@@ -4599,23 +4635,23 @@
         <v>2045</v>
       </c>
       <c r="B58" s="1">
-        <f>+[1]Summary!C178</f>
-        <v>7692.8434632824201</v>
+        <f>+[2]Summary!C178</f>
+        <v>8321.1767966157531</v>
       </c>
       <c r="C58" s="1">
-        <f>+[1]Summary!D178</f>
+        <f>+[2]Summary!D178</f>
         <v>550.35983355835356</v>
       </c>
       <c r="D58" s="1">
-        <f>+[1]Summary!E178</f>
-        <v>628.33333333333337</v>
+        <f>+[2]Summary!E178</f>
+        <v>0</v>
       </c>
       <c r="E58" s="1">
-        <f>+[1]Summary!F178</f>
+        <f>+[2]Summary!F178</f>
         <v>20.858051387727865</v>
       </c>
       <c r="F58" s="1">
-        <f>+[1]Summary!G178</f>
+        <f>+[2]Summary!G178</f>
         <v>46.669281563948786</v>
       </c>
       <c r="G58" s="1">
@@ -4634,28 +4670,28 @@
         <v>2046</v>
       </c>
       <c r="B59" s="1">
-        <f>+[1]Summary!C179</f>
-        <v>7746.5600700967589</v>
+        <f>+[2]Summary!C179</f>
+        <v>8399.2267367634267</v>
       </c>
       <c r="C59" s="1">
-        <f>+[1]Summary!D179</f>
+        <f>+[2]Summary!D179</f>
         <v>539.35263688718646</v>
       </c>
       <c r="D59" s="1">
-        <f>+[1]Summary!E179</f>
-        <v>652.66666666666663</v>
+        <f>+[2]Summary!E179</f>
+        <v>0</v>
       </c>
       <c r="E59" s="1">
-        <f>+[1]Summary!F179</f>
+        <f>+[2]Summary!F179</f>
         <v>21.801806801982551</v>
       </c>
       <c r="F59" s="1">
-        <f>+[1]Summary!G179</f>
+        <f>+[2]Summary!G179</f>
         <v>46.202588748309296</v>
       </c>
       <c r="G59" s="1">
         <f t="shared" si="0"/>
-        <v>9006.5837692009027</v>
+        <v>9006.5837692009045</v>
       </c>
       <c r="H59" t="s">
         <v>7</v>
@@ -4669,28 +4705,28 @@
         <v>2047</v>
       </c>
       <c r="B60" s="1">
-        <f>+[1]Summary!C180</f>
-        <v>7799.6417016808518</v>
+        <f>+[2]Summary!C180</f>
+        <v>8476.64170168085</v>
       </c>
       <c r="C60" s="1">
-        <f>+[1]Summary!D180</f>
+        <f>+[2]Summary!D180</f>
         <v>528.56558414944266</v>
       </c>
       <c r="D60" s="1">
-        <f>+[1]Summary!E180</f>
-        <v>677</v>
+        <f>+[2]Summary!E180</f>
+        <v>0</v>
       </c>
       <c r="E60" s="1">
-        <f>+[1]Summary!F180</f>
+        <f>+[2]Summary!F180</f>
         <v>22.766654016862141</v>
       </c>
       <c r="F60" s="1">
-        <f>+[1]Summary!G180</f>
+        <f>+[2]Summary!G180</f>
         <v>45.740562860826209</v>
       </c>
       <c r="G60" s="1">
         <f t="shared" si="0"/>
-        <v>9073.7145027079841</v>
+        <v>9073.7145027079823</v>
       </c>
       <c r="H60" t="s">
         <v>7</v>
@@ -4704,23 +4740,23 @@
         <v>2048</v>
       </c>
       <c r="B61" s="1">
-        <f>+[1]Summary!C181</f>
-        <v>7852.1228161175522</v>
+        <f>+[2]Summary!C181</f>
+        <v>8553.4561494508853</v>
       </c>
       <c r="C61" s="1">
-        <f>+[1]Summary!D181</f>
+        <f>+[2]Summary!D181</f>
         <v>517.99427246645382</v>
       </c>
       <c r="D61" s="1">
-        <f>+[1]Summary!E181</f>
-        <v>701.33333333333337</v>
+        <f>+[2]Summary!E181</f>
+        <v>0</v>
       </c>
       <c r="E61" s="1">
-        <f>+[1]Summary!F181</f>
+        <f>+[2]Summary!F181</f>
         <v>23.752627320833305</v>
       </c>
       <c r="F61" s="1">
-        <f>+[1]Summary!G181</f>
+        <f>+[2]Summary!G181</f>
         <v>45.283157232217938</v>
       </c>
       <c r="G61" s="1">
@@ -4739,28 +4775,28 @@
         <v>2049</v>
       </c>
       <c r="B62" s="1">
-        <f>+[1]Summary!C182</f>
-        <v>7904.0379713283182</v>
+        <f>+[2]Summary!C182</f>
+        <v>8629.7046379949861</v>
       </c>
       <c r="C62" s="1">
-        <f>+[1]Summary!D182</f>
+        <f>+[2]Summary!D182</f>
         <v>507.63438701712477</v>
       </c>
       <c r="D62" s="1">
-        <f>+[1]Summary!E182</f>
-        <v>725.66666666666663</v>
+        <f>+[2]Summary!E182</f>
+        <v>0</v>
       </c>
       <c r="E62" s="1">
-        <f>+[1]Summary!F182</f>
+        <f>+[2]Summary!F182</f>
         <v>24.759756667909301</v>
       </c>
       <c r="F62" s="1">
-        <f>+[1]Summary!G182</f>
+        <f>+[2]Summary!G182</f>
         <v>44.830325659895756</v>
       </c>
       <c r="G62" s="1">
         <f t="shared" si="0"/>
-        <v>9206.9291073399127</v>
+        <v>9206.9291073399145</v>
       </c>
       <c r="H62" t="s">
         <v>7</v>
@@ -4774,23 +4810,23 @@
         <v>2050</v>
       </c>
       <c r="B63" s="1">
-        <f>+[1]Summary!C183</f>
-        <v>7955.4218356042229</v>
+        <f>+[2]Summary!C183</f>
+        <v>8705.421835604222</v>
       </c>
       <c r="C63" s="1">
-        <f>+[1]Summary!D183</f>
+        <f>+[2]Summary!D183</f>
         <v>497.48169927678225</v>
       </c>
       <c r="D63" s="1">
-        <f>+[1]Summary!E183</f>
-        <v>750</v>
+        <f>+[2]Summary!E183</f>
+        <v>0</v>
       </c>
       <c r="E63" s="1">
-        <f>+[1]Summary!F183</f>
+        <f>+[2]Summary!F183</f>
         <v>25.788067748059987</v>
       </c>
       <c r="F63" s="1">
-        <f>+[1]Summary!G183</f>
+        <f>+[2]Summary!G183</f>
         <v>44.382022403296808</v>
       </c>
       <c r="G63" s="1">
